--- a/upload/programa2026.xlsx
+++ b/upload/programa2026.xlsx
@@ -9,17 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="programa" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -3566,11 +3561,9 @@
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -3926,7 +3919,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L981"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="129.28515625" customWidth="1"/>
@@ -4005,7 +3998,7 @@
         <v>1219310.69</v>
       </c>
       <c r="I2" s="5">
-        <v>973986.93</v>
+        <v>977155.93</v>
       </c>
       <c r="J2" s="5">
         <v>965533.8</v>
@@ -4398,10 +4391,10 @@
         <v>15</v>
       </c>
       <c r="H14" s="5">
-        <v>57271.48</v>
+        <v>57291.48</v>
       </c>
       <c r="I14" s="5">
-        <v>37509.550000000003</v>
+        <v>40527.339999999997</v>
       </c>
       <c r="J14" s="5">
         <v>37108.15</v>
@@ -4436,10 +4429,10 @@
         <v>15</v>
       </c>
       <c r="H15" s="5">
-        <v>57271.48</v>
+        <v>57291.48</v>
       </c>
       <c r="I15" s="5">
-        <v>37509.550000000003</v>
+        <v>40527.339999999997</v>
       </c>
       <c r="J15" s="5">
         <v>37108.15</v>
@@ -4538,10 +4531,10 @@
         <v>15</v>
       </c>
       <c r="H18" s="5">
-        <v>168628.42</v>
+        <v>168691.8</v>
       </c>
       <c r="I18" s="5">
-        <v>143067.78</v>
+        <v>146333.76000000001</v>
       </c>
       <c r="J18" s="5">
         <v>142568.48000000001</v>
@@ -4576,10 +4569,10 @@
         <v>15</v>
       </c>
       <c r="H19" s="5">
-        <v>168628.42</v>
+        <v>168691.8</v>
       </c>
       <c r="I19" s="5">
-        <v>143067.78</v>
+        <v>146333.76000000001</v>
       </c>
       <c r="J19" s="5">
         <v>142568.48000000001</v>
@@ -4710,13 +4703,13 @@
         <v>23</v>
       </c>
       <c r="H23" s="5">
-        <v>392108514.56</v>
+        <v>393433927.91000003</v>
       </c>
       <c r="I23" s="5">
-        <v>385723045.27999997</v>
+        <v>387033872.41000003</v>
       </c>
       <c r="J23" s="5">
-        <v>377256585.74000001</v>
+        <v>378564021.12</v>
       </c>
       <c r="K23" s="5">
         <v>4102443.76</v>
@@ -4748,13 +4741,13 @@
         <v>23</v>
       </c>
       <c r="H24" s="5">
-        <v>392108514.56</v>
+        <v>393433927.91000003</v>
       </c>
       <c r="I24" s="5">
-        <v>385723045.27999997</v>
+        <v>387033872.41000003</v>
       </c>
       <c r="J24" s="5">
-        <v>377256585.74000001</v>
+        <v>378564021.12</v>
       </c>
       <c r="K24" s="5">
         <v>549554.03</v>
@@ -4786,13 +4779,13 @@
         <v>65</v>
       </c>
       <c r="H25" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I25" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J25" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K25" s="5">
         <v>2393724.37</v>
@@ -4824,13 +4817,13 @@
         <v>65</v>
       </c>
       <c r="H26" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I26" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J26" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K26" s="5">
         <v>1469.36</v>
@@ -4862,13 +4855,13 @@
         <v>65</v>
       </c>
       <c r="H27" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I27" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J27" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K27" s="5">
         <v>68350.28</v>
@@ -4900,13 +4893,13 @@
         <v>65</v>
       </c>
       <c r="H28" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I28" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J28" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K28" s="5">
         <v>28599.78</v>
@@ -4938,19 +4931,19 @@
         <v>65</v>
       </c>
       <c r="H29" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I29" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J29" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K29" s="5">
-        <v>6016252.6399999997</v>
+        <v>6051763.5999999996</v>
       </c>
       <c r="L29" s="6">
-        <v>5575928.71</v>
+        <v>5609735.1399999997</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -4976,13 +4969,13 @@
         <v>65</v>
       </c>
       <c r="H30" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I30" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J30" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K30" s="5">
         <v>10955801.24</v>
@@ -5014,13 +5007,13 @@
         <v>65</v>
       </c>
       <c r="H31" s="5">
-        <v>41836366.030000001</v>
+        <v>42210096.159999996</v>
       </c>
       <c r="I31" s="5">
-        <v>25251158.41</v>
+        <v>26212061.530000001</v>
       </c>
       <c r="J31" s="5">
-        <v>21955757.449999999</v>
+        <v>22924662.329999998</v>
       </c>
       <c r="K31" s="5">
         <v>1254693.33</v>
@@ -5122,7 +5115,7 @@
         <v>12275753.09</v>
       </c>
       <c r="J34" s="5">
-        <v>10307684.27</v>
+        <v>10245743.130000001</v>
       </c>
       <c r="K34" s="5">
         <v>1977286.82</v>
@@ -5160,7 +5153,7 @@
         <v>12275753.09</v>
       </c>
       <c r="J35" s="5">
-        <v>10307684.27</v>
+        <v>10245743.130000001</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
@@ -5195,10 +5188,10 @@
         <v>238804</v>
       </c>
       <c r="I36" s="5">
-        <v>132007.37</v>
+        <v>151205.25</v>
       </c>
       <c r="J36" s="5">
-        <v>125364.89</v>
+        <v>142902.15</v>
       </c>
       <c r="K36" s="5">
         <v>30324.78</v>
@@ -5664,13 +5657,13 @@
         <v>109</v>
       </c>
       <c r="H50" s="5">
-        <v>4026881.15</v>
+        <v>4031481.65</v>
       </c>
       <c r="I50" s="5">
-        <v>3602019.94</v>
+        <v>3622537.07</v>
       </c>
       <c r="J50" s="5">
-        <v>3391974.61</v>
+        <v>3411551.17</v>
       </c>
       <c r="K50" s="5">
         <v>782610.17</v>
@@ -5702,13 +5695,13 @@
         <v>109</v>
       </c>
       <c r="H51" s="5">
-        <v>4026881.15</v>
+        <v>4031481.65</v>
       </c>
       <c r="I51" s="5">
-        <v>3602019.94</v>
+        <v>3622537.07</v>
       </c>
       <c r="J51" s="5">
-        <v>3391974.61</v>
+        <v>3411551.17</v>
       </c>
       <c r="K51" s="5">
         <v>13294.03</v>
@@ -6060,16 +6053,16 @@
         <v>132</v>
       </c>
       <c r="H62" s="5">
-        <v>71392381.680000007</v>
+        <v>74492772.599999994</v>
       </c>
       <c r="I62" s="5">
-        <v>17790330.75</v>
+        <v>18303772.949999999</v>
       </c>
       <c r="J62" s="5">
         <v>16265105.59</v>
       </c>
       <c r="K62" s="5">
-        <v>54624593.350000001</v>
+        <v>55224413.770000003</v>
       </c>
       <c r="L62" s="6">
         <v>49995741.520000003</v>
@@ -6098,10 +6091,10 @@
         <v>132</v>
       </c>
       <c r="H63" s="5">
-        <v>71392381.680000007</v>
+        <v>74492772.599999994</v>
       </c>
       <c r="I63" s="5">
-        <v>17790330.75</v>
+        <v>18303772.949999999</v>
       </c>
       <c r="J63" s="5">
         <v>16265105.59</v>
@@ -6136,10 +6129,10 @@
         <v>132</v>
       </c>
       <c r="H64" s="5">
-        <v>71392381.680000007</v>
+        <v>74492772.599999994</v>
       </c>
       <c r="I64" s="5">
-        <v>17790330.75</v>
+        <v>18303772.949999999</v>
       </c>
       <c r="J64" s="5">
         <v>16265105.59</v>
@@ -6174,13 +6167,13 @@
         <v>30</v>
       </c>
       <c r="H65" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I65" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J65" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K65" s="5">
         <v>1389461.04</v>
@@ -6212,13 +6205,13 @@
         <v>30</v>
       </c>
       <c r="H66" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I66" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J66" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K66" s="5">
         <v>0</v>
@@ -6250,13 +6243,13 @@
         <v>30</v>
       </c>
       <c r="H67" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I67" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J67" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K67" s="5">
         <v>9942378.0199999996</v>
@@ -6288,13 +6281,13 @@
         <v>30</v>
       </c>
       <c r="H68" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I68" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J68" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K68" s="5">
         <v>0</v>
@@ -6326,13 +6319,13 @@
         <v>30</v>
       </c>
       <c r="H69" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I69" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J69" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K69" s="5">
         <v>13198366.609999999</v>
@@ -6364,13 +6357,13 @@
         <v>30</v>
       </c>
       <c r="H70" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I70" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J70" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K70" s="5">
         <v>3889.11</v>
@@ -6402,13 +6395,13 @@
         <v>30</v>
       </c>
       <c r="H71" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I71" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J71" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K71" s="5">
         <v>2269462.52</v>
@@ -6440,13 +6433,13 @@
         <v>30</v>
       </c>
       <c r="H72" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I72" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J72" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K72" s="5">
         <v>7995977.2999999998</v>
@@ -6478,13 +6471,13 @@
         <v>30</v>
       </c>
       <c r="H73" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I73" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J73" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K73" s="5">
         <v>0</v>
@@ -6516,19 +6509,19 @@
         <v>30</v>
       </c>
       <c r="H74" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I74" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J74" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K74" s="5">
-        <v>29307852.010000002</v>
+        <v>29362029.129999999</v>
       </c>
       <c r="L74" s="6">
-        <v>27434822.82</v>
+        <v>27441501.699999999</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -6554,13 +6547,13 @@
         <v>30</v>
       </c>
       <c r="H75" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I75" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J75" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K75" s="5">
         <v>684</v>
@@ -6592,19 +6585,19 @@
         <v>30</v>
       </c>
       <c r="H76" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I76" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J76" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K76" s="5">
-        <v>22430907.460000001</v>
+        <v>22449991.699999999</v>
       </c>
       <c r="L76" s="6">
-        <v>23302599.109999999</v>
+        <v>23317593.350000001</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -6630,13 +6623,13 @@
         <v>30</v>
       </c>
       <c r="H77" s="5">
-        <v>372273082.19999999</v>
+        <v>381893215.63</v>
       </c>
       <c r="I77" s="5">
-        <v>287849730.02999997</v>
+        <v>293381836.92000002</v>
       </c>
       <c r="J77" s="5">
-        <v>248785852.69</v>
+        <v>251207687.80000001</v>
       </c>
       <c r="K77" s="5">
         <v>275795.52</v>
@@ -7055,10 +7048,10 @@
         <v>6252164.75</v>
       </c>
       <c r="I90" s="5">
-        <v>3140431.12</v>
+        <v>3143803.57</v>
       </c>
       <c r="J90" s="5">
-        <v>1435747.84</v>
+        <v>2937894.64</v>
       </c>
       <c r="K90" s="5">
         <v>277082.09999999998</v>
@@ -7093,10 +7086,10 @@
         <v>6252164.75</v>
       </c>
       <c r="I91" s="5">
-        <v>3140431.12</v>
+        <v>3143803.57</v>
       </c>
       <c r="J91" s="5">
-        <v>1435747.84</v>
+        <v>2937894.64</v>
       </c>
       <c r="K91" s="5">
         <v>3439.22</v>
@@ -7131,10 +7124,10 @@
         <v>6252164.75</v>
       </c>
       <c r="I92" s="5">
-        <v>3140431.12</v>
+        <v>3143803.57</v>
       </c>
       <c r="J92" s="5">
-        <v>1435747.84</v>
+        <v>2937894.64</v>
       </c>
       <c r="K92" s="5">
         <v>748174.5</v>
@@ -7166,13 +7159,13 @@
         <v>19</v>
       </c>
       <c r="H93" s="5">
-        <v>217434745.03</v>
+        <v>217514588.46000001</v>
       </c>
       <c r="I93" s="5">
-        <v>161183490.41999999</v>
+        <v>162020073.84999999</v>
       </c>
       <c r="J93" s="5">
-        <v>158166513.47999999</v>
+        <v>158171963.47999999</v>
       </c>
       <c r="K93" s="5">
         <v>19292.990000000002</v>
@@ -7204,13 +7197,13 @@
         <v>19</v>
       </c>
       <c r="H94" s="5">
-        <v>217434745.03</v>
+        <v>217514588.46000001</v>
       </c>
       <c r="I94" s="5">
-        <v>161183490.41999999</v>
+        <v>162020073.84999999</v>
       </c>
       <c r="J94" s="5">
-        <v>158166513.47999999</v>
+        <v>158171963.47999999</v>
       </c>
       <c r="K94" s="5">
         <v>72975.600000000006</v>
@@ -7242,13 +7235,13 @@
         <v>19</v>
       </c>
       <c r="H95" s="5">
-        <v>217434745.03</v>
+        <v>217514588.46000001</v>
       </c>
       <c r="I95" s="5">
-        <v>161183490.41999999</v>
+        <v>162020073.84999999</v>
       </c>
       <c r="J95" s="5">
-        <v>158166513.47999999</v>
+        <v>158171963.47999999</v>
       </c>
       <c r="K95" s="5">
         <v>182366.26</v>
@@ -7280,13 +7273,13 @@
         <v>19</v>
       </c>
       <c r="H96" s="5">
-        <v>217434745.03</v>
+        <v>217514588.46000001</v>
       </c>
       <c r="I96" s="5">
-        <v>161183490.41999999</v>
+        <v>162020073.84999999</v>
       </c>
       <c r="J96" s="5">
-        <v>158166513.47999999</v>
+        <v>158171963.47999999</v>
       </c>
       <c r="K96" s="5">
         <v>518494.9</v>
@@ -7478,13 +7471,13 @@
         <v>170</v>
       </c>
       <c r="H102" s="5">
-        <v>2152217.4900000002</v>
+        <v>2152999.7400000002</v>
       </c>
       <c r="I102" s="5">
-        <v>1870222.68</v>
+        <v>1953478.46</v>
       </c>
       <c r="J102" s="5">
-        <v>1674046.65</v>
+        <v>1690145.54</v>
       </c>
       <c r="K102" s="5">
         <v>344863.67</v>
@@ -7548,13 +7541,13 @@
         <v>163</v>
       </c>
       <c r="H104" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I104" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J104" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K104" s="5">
         <v>15870452.77</v>
@@ -7586,13 +7579,13 @@
         <v>163</v>
       </c>
       <c r="H105" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I105" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J105" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K105" s="5">
         <v>1235094.52</v>
@@ -7624,13 +7617,13 @@
         <v>163</v>
       </c>
       <c r="H106" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I106" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J106" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K106" s="5">
         <v>9240.64</v>
@@ -7662,13 +7655,13 @@
         <v>163</v>
       </c>
       <c r="H107" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I107" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J107" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K107" s="5">
         <v>64158.12</v>
@@ -7700,13 +7693,13 @@
         <v>163</v>
       </c>
       <c r="H108" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I108" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J108" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K108" s="5">
         <v>131525.41</v>
@@ -7738,13 +7731,13 @@
         <v>163</v>
       </c>
       <c r="H109" s="5">
-        <v>52970312.25</v>
+        <v>52978637.649999999</v>
       </c>
       <c r="I109" s="5">
-        <v>32643276.140000001</v>
+        <v>33559913.880000003</v>
       </c>
       <c r="J109" s="5">
-        <v>29903405.300000001</v>
+        <v>30667091.890000001</v>
       </c>
       <c r="K109" s="5">
         <v>309963.82</v>
@@ -7954,7 +7947,7 @@
         <v>212</v>
       </c>
       <c r="H115" s="5">
-        <v>1736221.01</v>
+        <v>1799021.01</v>
       </c>
       <c r="I115" s="5">
         <v>1124101.0900000001</v>
@@ -7992,7 +7985,7 @@
         <v>212</v>
       </c>
       <c r="H116" s="5">
-        <v>1736221.01</v>
+        <v>1799021.01</v>
       </c>
       <c r="I116" s="5">
         <v>1124101.0900000001</v>
@@ -8158,7 +8151,7 @@
         <v>225</v>
       </c>
       <c r="H121" s="5">
-        <v>6233428.6699999999</v>
+        <v>6006810.9199999999</v>
       </c>
       <c r="I121" s="5">
         <v>3950518.35</v>
@@ -8196,7 +8189,7 @@
         <v>225</v>
       </c>
       <c r="H122" s="5">
-        <v>6233428.6699999999</v>
+        <v>6006810.9199999999</v>
       </c>
       <c r="I122" s="5">
         <v>3950518.35</v>
@@ -8234,13 +8227,13 @@
         <v>230</v>
       </c>
       <c r="H123" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I123" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J123" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K123" s="5">
         <v>4039.43</v>
@@ -8272,13 +8265,13 @@
         <v>230</v>
       </c>
       <c r="H124" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I124" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J124" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K124" s="5">
         <v>103127.22</v>
@@ -8310,13 +8303,13 @@
         <v>230</v>
       </c>
       <c r="H125" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I125" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J125" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K125" s="5">
         <v>297682.68</v>
@@ -8348,13 +8341,13 @@
         <v>230</v>
       </c>
       <c r="H126" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I126" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J126" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K126" s="5">
         <v>495864.7</v>
@@ -8386,13 +8379,13 @@
         <v>230</v>
       </c>
       <c r="H127" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I127" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J127" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K127" s="5">
         <v>3421283.04</v>
@@ -8462,13 +8455,13 @@
         <v>230</v>
       </c>
       <c r="H129" s="5">
-        <v>29203798.719999999</v>
+        <v>29555250.420000002</v>
       </c>
       <c r="I129" s="5">
-        <v>19598307.829999998</v>
+        <v>20357425.289999999</v>
       </c>
       <c r="J129" s="5">
-        <v>16596416.17</v>
+        <v>16921316.399999999</v>
       </c>
       <c r="K129" s="5">
         <v>0</v>
@@ -8500,13 +8493,13 @@
         <v>45</v>
       </c>
       <c r="H130" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I130" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J130" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K130" s="5">
         <v>151216.29999999999</v>
@@ -8538,13 +8531,13 @@
         <v>45</v>
       </c>
       <c r="H131" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I131" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J131" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K131" s="5">
         <v>0</v>
@@ -8576,13 +8569,13 @@
         <v>45</v>
       </c>
       <c r="H132" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I132" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J132" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K132" s="5">
         <v>3670599.72</v>
@@ -8614,19 +8607,19 @@
         <v>45</v>
       </c>
       <c r="H133" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I133" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J133" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K133" s="5">
         <v>15154983.449999999</v>
       </c>
       <c r="L133" s="6">
-        <v>18660420.18</v>
+        <v>18662820.100000001</v>
       </c>
     </row>
     <row r="134" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -8652,13 +8645,13 @@
         <v>45</v>
       </c>
       <c r="H134" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I134" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J134" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K134" s="5">
         <v>1506750.42</v>
@@ -8690,13 +8683,13 @@
         <v>45</v>
       </c>
       <c r="H135" s="5">
-        <v>102814184.84</v>
+        <v>103790471.06</v>
       </c>
       <c r="I135" s="5">
-        <v>55451159.450000003</v>
+        <v>56814267.189999998</v>
       </c>
       <c r="J135" s="5">
-        <v>34414173.909999996</v>
+        <v>34528589.280000001</v>
       </c>
       <c r="K135" s="5">
         <v>1752763.8</v>
@@ -8728,13 +8721,13 @@
         <v>114</v>
       </c>
       <c r="H136" s="5">
-        <v>85954189.560000002</v>
+        <v>86615970.560000002</v>
       </c>
       <c r="I136" s="5">
-        <v>46333835.939999998</v>
+        <v>46334304.840000004</v>
       </c>
       <c r="J136" s="5">
-        <v>31500648.07</v>
+        <v>32175145.75</v>
       </c>
       <c r="K136" s="5">
         <v>1195528.56</v>
@@ -8766,13 +8759,13 @@
         <v>114</v>
       </c>
       <c r="H137" s="5">
-        <v>85954189.560000002</v>
+        <v>86615970.560000002</v>
       </c>
       <c r="I137" s="5">
-        <v>46333835.939999998</v>
+        <v>46334304.840000004</v>
       </c>
       <c r="J137" s="5">
-        <v>31500648.07</v>
+        <v>32175145.75</v>
       </c>
       <c r="K137" s="5">
         <v>1147800</v>
@@ -8804,13 +8797,13 @@
         <v>114</v>
       </c>
       <c r="H138" s="5">
-        <v>85954189.560000002</v>
+        <v>86615970.560000002</v>
       </c>
       <c r="I138" s="5">
-        <v>46333835.939999998</v>
+        <v>46334304.840000004</v>
       </c>
       <c r="J138" s="5">
-        <v>31500648.07</v>
+        <v>32175145.75</v>
       </c>
       <c r="K138" s="5">
         <v>5816039.8600000003</v>
@@ -8842,19 +8835,19 @@
         <v>114</v>
       </c>
       <c r="H139" s="5">
-        <v>85954189.560000002</v>
+        <v>86615970.560000002</v>
       </c>
       <c r="I139" s="5">
-        <v>46333835.939999998</v>
+        <v>46334304.840000004</v>
       </c>
       <c r="J139" s="5">
-        <v>31500648.07</v>
+        <v>32175145.75</v>
       </c>
       <c r="K139" s="5">
         <v>20740086.300000001</v>
       </c>
       <c r="L139" s="6">
-        <v>22865741.280000001</v>
+        <v>23819294.620000001</v>
       </c>
     </row>
     <row r="140" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -8880,13 +8873,13 @@
         <v>114</v>
       </c>
       <c r="H140" s="5">
-        <v>85954189.560000002</v>
+        <v>86615970.560000002</v>
       </c>
       <c r="I140" s="5">
-        <v>46333835.939999998</v>
+        <v>46334304.840000004</v>
       </c>
       <c r="J140" s="5">
-        <v>31500648.07</v>
+        <v>32175145.75</v>
       </c>
       <c r="K140" s="5">
         <v>12093348.48</v>
@@ -9151,7 +9144,7 @@
         <v>36403270.719999999</v>
       </c>
       <c r="I148" s="5">
-        <v>30778586.5</v>
+        <v>30832854.539999999</v>
       </c>
       <c r="J148" s="5">
         <v>29611534.539999999</v>
@@ -9189,7 +9182,7 @@
         <v>36403270.719999999</v>
       </c>
       <c r="I149" s="5">
-        <v>30778586.5</v>
+        <v>30832854.539999999</v>
       </c>
       <c r="J149" s="5">
         <v>29611534.539999999</v>
@@ -9291,7 +9284,7 @@
         <v>2365864.98</v>
       </c>
       <c r="I152" s="5">
-        <v>1067498.69</v>
+        <v>1103170.8799999999</v>
       </c>
       <c r="J152" s="5">
         <v>885147.37</v>
@@ -9329,7 +9322,7 @@
         <v>2365864.98</v>
       </c>
       <c r="I153" s="5">
-        <v>1067498.69</v>
+        <v>1103170.8799999999</v>
       </c>
       <c r="J153" s="5">
         <v>885147.37</v>
@@ -9367,7 +9360,7 @@
         <v>2365864.98</v>
       </c>
       <c r="I154" s="5">
-        <v>1067498.69</v>
+        <v>1103170.8799999999</v>
       </c>
       <c r="J154" s="5">
         <v>885147.37</v>
@@ -9402,13 +9395,13 @@
         <v>114</v>
       </c>
       <c r="H155" s="5">
-        <v>59194272.289999999</v>
+        <v>59284272.289999999</v>
       </c>
       <c r="I155" s="5">
-        <v>32732564.25</v>
+        <v>34354872.399999999</v>
       </c>
       <c r="J155" s="5">
-        <v>32008384.030000001</v>
+        <v>32082043.449999999</v>
       </c>
       <c r="K155" s="5">
         <v>0</v>
@@ -9440,13 +9433,13 @@
         <v>114</v>
       </c>
       <c r="H156" s="5">
-        <v>59194272.289999999</v>
+        <v>59284272.289999999</v>
       </c>
       <c r="I156" s="5">
-        <v>32732564.25</v>
+        <v>34354872.399999999</v>
       </c>
       <c r="J156" s="5">
-        <v>32008384.030000001</v>
+        <v>32082043.449999999</v>
       </c>
       <c r="K156" s="5">
         <v>2717127.41</v>
@@ -9478,13 +9471,13 @@
         <v>114</v>
       </c>
       <c r="H157" s="5">
-        <v>59194272.289999999</v>
+        <v>59284272.289999999</v>
       </c>
       <c r="I157" s="5">
-        <v>32732564.25</v>
+        <v>34354872.399999999</v>
       </c>
       <c r="J157" s="5">
-        <v>32008384.030000001</v>
+        <v>32082043.449999999</v>
       </c>
       <c r="K157" s="5">
         <v>207340.35</v>
@@ -9516,13 +9509,13 @@
         <v>114</v>
       </c>
       <c r="H158" s="5">
-        <v>59194272.289999999</v>
+        <v>59284272.289999999</v>
       </c>
       <c r="I158" s="5">
-        <v>32732564.25</v>
+        <v>34354872.399999999</v>
       </c>
       <c r="J158" s="5">
-        <v>32008384.030000001</v>
+        <v>32082043.449999999</v>
       </c>
       <c r="K158" s="5">
         <v>5897196.0599999996</v>
@@ -9554,13 +9547,13 @@
         <v>114</v>
       </c>
       <c r="H159" s="5">
-        <v>59194272.289999999</v>
+        <v>59284272.289999999</v>
       </c>
       <c r="I159" s="5">
-        <v>32732564.25</v>
+        <v>34354872.399999999</v>
       </c>
       <c r="J159" s="5">
-        <v>32008384.030000001</v>
+        <v>32082043.449999999</v>
       </c>
       <c r="K159" s="5">
         <v>171674.43</v>
@@ -9592,13 +9585,13 @@
         <v>105</v>
       </c>
       <c r="H160" s="5">
-        <v>647332691.23000002</v>
+        <v>647502426.02999997</v>
       </c>
       <c r="I160" s="5">
-        <v>331077835.69999999</v>
+        <v>338553722.38</v>
       </c>
       <c r="J160" s="5">
-        <v>327133086.92000002</v>
+        <v>335015362.89999998</v>
       </c>
       <c r="K160" s="5">
         <v>2533169.13</v>
@@ -9630,13 +9623,13 @@
         <v>105</v>
       </c>
       <c r="H161" s="5">
-        <v>647332691.23000002</v>
+        <v>647502426.02999997</v>
       </c>
       <c r="I161" s="5">
-        <v>331077835.69999999</v>
+        <v>338553722.38</v>
       </c>
       <c r="J161" s="5">
-        <v>327133086.92000002</v>
+        <v>335015362.89999998</v>
       </c>
       <c r="K161" s="5">
         <v>979414.02</v>
@@ -9668,19 +9661,19 @@
         <v>105</v>
       </c>
       <c r="H162" s="5">
-        <v>647332691.23000002</v>
+        <v>647502426.02999997</v>
       </c>
       <c r="I162" s="5">
-        <v>331077835.69999999</v>
+        <v>338553722.38</v>
       </c>
       <c r="J162" s="5">
-        <v>327133086.92000002</v>
+        <v>335015362.89999998</v>
       </c>
       <c r="K162" s="5">
-        <v>84538593.040000007</v>
+        <v>84539865.150000006</v>
       </c>
       <c r="L162" s="6">
-        <v>84133522.120000005</v>
+        <v>84134794.230000004</v>
       </c>
     </row>
     <row r="163" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -9706,13 +9699,13 @@
         <v>105</v>
       </c>
       <c r="H163" s="5">
-        <v>647332691.23000002</v>
+        <v>647502426.02999997</v>
       </c>
       <c r="I163" s="5">
-        <v>331077835.69999999</v>
+        <v>338553722.38</v>
       </c>
       <c r="J163" s="5">
-        <v>327133086.92000002</v>
+        <v>335015362.89999998</v>
       </c>
       <c r="K163" s="5">
         <v>37887250.729999997</v>
@@ -9744,13 +9737,13 @@
         <v>105</v>
       </c>
       <c r="H164" s="5">
-        <v>647332691.23000002</v>
+        <v>647502426.02999997</v>
       </c>
       <c r="I164" s="5">
-        <v>331077835.69999999</v>
+        <v>338553722.38</v>
       </c>
       <c r="J164" s="5">
-        <v>327133086.92000002</v>
+        <v>335015362.89999998</v>
       </c>
       <c r="K164" s="5">
         <v>11352935.92</v>
@@ -9814,7 +9807,7 @@
         <v>292</v>
       </c>
       <c r="H166" s="5">
-        <v>100955.39</v>
+        <v>322562.53000000003</v>
       </c>
       <c r="I166" s="5">
         <v>78867.83</v>
@@ -9852,7 +9845,7 @@
         <v>292</v>
       </c>
       <c r="H167" s="5">
-        <v>100955.39</v>
+        <v>322562.53000000003</v>
       </c>
       <c r="I167" s="5">
         <v>78867.83</v>
@@ -9957,10 +9950,10 @@
         <v>561213.1</v>
       </c>
       <c r="I170" s="5">
-        <v>465252.5</v>
+        <v>474305.5</v>
       </c>
       <c r="J170" s="5">
-        <v>302590.28000000003</v>
+        <v>304405.08</v>
       </c>
       <c r="K170" s="5">
         <v>198090.48</v>
@@ -9995,10 +9988,10 @@
         <v>561213.1</v>
       </c>
       <c r="I171" s="5">
-        <v>465252.5</v>
+        <v>474305.5</v>
       </c>
       <c r="J171" s="5">
-        <v>302590.28000000003</v>
+        <v>304405.08</v>
       </c>
       <c r="K171" s="5">
         <v>0</v>
@@ -10033,10 +10026,10 @@
         <v>11324376.84</v>
       </c>
       <c r="I172" s="5">
-        <v>10726165.949999999</v>
+        <v>10732744.050000001</v>
       </c>
       <c r="J172" s="5">
-        <v>10683634.210000001</v>
+        <v>10704888.15</v>
       </c>
       <c r="K172" s="5">
         <v>55710.65</v>
@@ -10071,10 +10064,10 @@
         <v>11324376.84</v>
       </c>
       <c r="I173" s="5">
-        <v>10726165.949999999</v>
+        <v>10732744.050000001</v>
       </c>
       <c r="J173" s="5">
-        <v>10683634.210000001</v>
+        <v>10704888.15</v>
       </c>
       <c r="K173" s="5">
         <v>33831.06</v>
@@ -10109,10 +10102,10 @@
         <v>11324376.84</v>
       </c>
       <c r="I174" s="5">
-        <v>10726165.949999999</v>
+        <v>10732744.050000001</v>
       </c>
       <c r="J174" s="5">
-        <v>10683634.210000001</v>
+        <v>10704888.15</v>
       </c>
       <c r="K174" s="5">
         <v>18480</v>
@@ -10147,10 +10140,10 @@
         <v>11324376.84</v>
       </c>
       <c r="I175" s="5">
-        <v>10726165.949999999</v>
+        <v>10732744.050000001</v>
       </c>
       <c r="J175" s="5">
-        <v>10683634.210000001</v>
+        <v>10704888.15</v>
       </c>
       <c r="K175" s="5">
         <v>439092.4</v>
@@ -10482,13 +10475,13 @@
         <v>310</v>
       </c>
       <c r="H185" s="5">
-        <v>14031668.4</v>
+        <v>14217222.84</v>
       </c>
       <c r="I185" s="5">
-        <v>6997868.2199999997</v>
+        <v>7191071.5800000001</v>
       </c>
       <c r="J185" s="5">
-        <v>6285371.1900000004</v>
+        <v>6286021.6900000004</v>
       </c>
       <c r="K185" s="5">
         <v>681026.76</v>
@@ -10520,13 +10513,13 @@
         <v>310</v>
       </c>
       <c r="H186" s="5">
-        <v>14031668.4</v>
+        <v>14217222.84</v>
       </c>
       <c r="I186" s="5">
-        <v>6997868.2199999997</v>
+        <v>7191071.5800000001</v>
       </c>
       <c r="J186" s="5">
-        <v>6285371.1900000004</v>
+        <v>6286021.6900000004</v>
       </c>
       <c r="K186" s="5">
         <v>607251.5</v>
@@ -10558,13 +10551,13 @@
         <v>310</v>
       </c>
       <c r="H187" s="5">
-        <v>14031668.4</v>
+        <v>14217222.84</v>
       </c>
       <c r="I187" s="5">
-        <v>6997868.2199999997</v>
+        <v>7191071.5800000001</v>
       </c>
       <c r="J187" s="5">
-        <v>6285371.1900000004</v>
+        <v>6286021.6900000004</v>
       </c>
       <c r="K187" s="5">
         <v>790397.5</v>
@@ -10884,13 +10877,13 @@
         <v>114</v>
       </c>
       <c r="H197" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I197" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J197" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K197" s="5">
         <v>2602500.4</v>
@@ -10922,13 +10915,13 @@
         <v>114</v>
       </c>
       <c r="H198" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I198" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J198" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K198" s="5">
         <v>98355.33</v>
@@ -10960,13 +10953,13 @@
         <v>114</v>
       </c>
       <c r="H199" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I199" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J199" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K199" s="5">
         <v>267.85000000000002</v>
@@ -10998,13 +10991,13 @@
         <v>114</v>
       </c>
       <c r="H200" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I200" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J200" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K200" s="5">
         <v>2224283.2599999998</v>
@@ -11036,13 +11029,13 @@
         <v>114</v>
       </c>
       <c r="H201" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I201" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J201" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K201" s="5">
         <v>56249.95</v>
@@ -11074,13 +11067,13 @@
         <v>114</v>
       </c>
       <c r="H202" s="5">
-        <v>16735915.109999999</v>
+        <v>16997634.57</v>
       </c>
       <c r="I202" s="5">
-        <v>11137655.25</v>
+        <v>11387598.220000001</v>
       </c>
       <c r="J202" s="5">
-        <v>8957591.8399999999</v>
+        <v>9153462.1799999997</v>
       </c>
       <c r="K202" s="5">
         <v>654967.76</v>
@@ -11185,7 +11178,7 @@
         <v>337445.46</v>
       </c>
       <c r="K205" s="5">
-        <v>1759211.94</v>
+        <v>1770445.43</v>
       </c>
       <c r="L205" s="6">
         <v>1382350.32</v>
@@ -11217,7 +11210,7 @@
         <v>19383250.43</v>
       </c>
       <c r="I206" s="5">
-        <v>14669678.720000001</v>
+        <v>14671478.720000001</v>
       </c>
       <c r="J206" s="5">
         <v>14242755.5</v>
@@ -11252,13 +11245,13 @@
         <v>262</v>
       </c>
       <c r="H207" s="5">
-        <v>3170207.31</v>
+        <v>3175452.48</v>
       </c>
       <c r="I207" s="5">
-        <v>1173502.6299999999</v>
+        <v>1181034.97</v>
       </c>
       <c r="J207" s="5">
-        <v>321422.88</v>
+        <v>324571.11</v>
       </c>
       <c r="K207" s="5">
         <v>814005.95</v>
@@ -11360,13 +11353,13 @@
         <v>262</v>
       </c>
       <c r="H210" s="5">
-        <v>13286291.33</v>
+        <v>13286004.33</v>
       </c>
       <c r="I210" s="5">
-        <v>7610486.6100000003</v>
+        <v>7610199.6100000003</v>
       </c>
       <c r="J210" s="5">
-        <v>6564297.2699999996</v>
+        <v>6601643.6699999999</v>
       </c>
       <c r="K210" s="5">
         <v>671893.92</v>
@@ -11558,13 +11551,13 @@
         <v>262</v>
       </c>
       <c r="H216" s="5">
-        <v>8500407.7200000007</v>
+        <v>8500265.6699999999</v>
       </c>
       <c r="I216" s="5">
-        <v>4823757.16</v>
+        <v>4823615.1100000003</v>
       </c>
       <c r="J216" s="5">
-        <v>4808631.9400000004</v>
+        <v>4810258.7699999996</v>
       </c>
       <c r="K216" s="5">
         <v>2650471.71</v>
@@ -11596,13 +11589,13 @@
         <v>262</v>
       </c>
       <c r="H217" s="5">
-        <v>8500407.7200000007</v>
+        <v>8500265.6699999999</v>
       </c>
       <c r="I217" s="5">
-        <v>4823757.16</v>
+        <v>4823615.1100000003</v>
       </c>
       <c r="J217" s="5">
-        <v>4808631.9400000004</v>
+        <v>4810258.7699999996</v>
       </c>
       <c r="K217" s="5">
         <v>6406030.7599999998</v>
@@ -11634,13 +11627,13 @@
         <v>262</v>
       </c>
       <c r="H218" s="5">
-        <v>8500407.7200000007</v>
+        <v>8500265.6699999999</v>
       </c>
       <c r="I218" s="5">
-        <v>4823757.16</v>
+        <v>4823615.1100000003</v>
       </c>
       <c r="J218" s="5">
-        <v>4808631.9400000004</v>
+        <v>4810258.7699999996</v>
       </c>
       <c r="K218" s="5">
         <v>87482.95</v>
@@ -11672,13 +11665,13 @@
         <v>262</v>
       </c>
       <c r="H219" s="5">
-        <v>8500407.7200000007</v>
+        <v>8500265.6699999999</v>
       </c>
       <c r="I219" s="5">
-        <v>4823757.16</v>
+        <v>4823615.1100000003</v>
       </c>
       <c r="J219" s="5">
-        <v>4808631.9400000004</v>
+        <v>4810258.7699999996</v>
       </c>
       <c r="K219" s="5">
         <v>0</v>
@@ -11710,13 +11703,13 @@
         <v>262</v>
       </c>
       <c r="H220" s="5">
-        <v>2030110.79</v>
+        <v>2058751.98</v>
       </c>
       <c r="I220" s="5">
         <v>1964259.73</v>
       </c>
       <c r="J220" s="5">
-        <v>1233812.47</v>
+        <v>1265891.58</v>
       </c>
       <c r="K220" s="5">
         <v>346238.83</v>
@@ -11908,13 +11901,13 @@
         <v>262</v>
       </c>
       <c r="H226" s="5">
-        <v>1961725.76</v>
+        <v>1984884.77</v>
       </c>
       <c r="I226" s="5">
-        <v>1865756.28</v>
+        <v>1893811.17</v>
       </c>
       <c r="J226" s="5">
-        <v>1874151.62</v>
+        <v>1920433.2</v>
       </c>
       <c r="K226" s="5">
         <v>239931.51</v>
@@ -12016,13 +12009,13 @@
         <v>381</v>
       </c>
       <c r="H229" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I229" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J229" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K229" s="5">
         <v>0</v>
@@ -12054,13 +12047,13 @@
         <v>381</v>
       </c>
       <c r="H230" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I230" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J230" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K230" s="5">
         <v>210703.22</v>
@@ -12092,13 +12085,13 @@
         <v>381</v>
       </c>
       <c r="H231" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I231" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J231" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K231" s="5">
         <v>747.12</v>
@@ -12130,16 +12123,16 @@
         <v>381</v>
       </c>
       <c r="H232" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I232" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J232" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K232" s="5">
-        <v>3022268.53</v>
+        <v>3026828.28</v>
       </c>
       <c r="L232" s="6">
         <v>2890731.12</v>
@@ -12168,13 +12161,13 @@
         <v>381</v>
       </c>
       <c r="H233" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I233" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J233" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K233" s="5">
         <v>4275098.54</v>
@@ -12206,19 +12199,19 @@
         <v>381</v>
       </c>
       <c r="H234" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I234" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J234" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K234" s="5">
-        <v>13516459.050000001</v>
+        <v>13517389.050000001</v>
       </c>
       <c r="L234" s="6">
-        <v>14424261.42</v>
+        <v>14440553.539999999</v>
       </c>
     </row>
     <row r="235" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -12244,13 +12237,13 @@
         <v>381</v>
       </c>
       <c r="H235" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I235" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J235" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K235" s="5">
         <v>320445.12</v>
@@ -12282,16 +12275,16 @@
         <v>381</v>
       </c>
       <c r="H236" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I236" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J236" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K236" s="5">
-        <v>3295766.16</v>
+        <v>3805996.73</v>
       </c>
       <c r="L236" s="6">
         <v>3141628.17</v>
@@ -12320,13 +12313,13 @@
         <v>381</v>
       </c>
       <c r="H237" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I237" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J237" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K237" s="5">
         <v>1626044.83</v>
@@ -12358,13 +12351,13 @@
         <v>381</v>
       </c>
       <c r="H238" s="5">
-        <v>520568208.06999999</v>
+        <v>520974516.77999997</v>
       </c>
       <c r="I238" s="5">
-        <v>497823042.00999999</v>
+        <v>498205850.07999998</v>
       </c>
       <c r="J238" s="5">
-        <v>496954017.76999998</v>
+        <v>496999903.51999998</v>
       </c>
       <c r="K238" s="5">
         <v>40648.160000000003</v>
@@ -12822,13 +12815,13 @@
         <v>35</v>
       </c>
       <c r="H251" s="5">
-        <v>2513456337.9000001</v>
+        <v>2508134931.52</v>
       </c>
       <c r="I251" s="5">
-        <v>1623074216.3699999</v>
+        <v>1651565693.1099999</v>
       </c>
       <c r="J251" s="5">
-        <v>1561628972.7</v>
+        <v>1563971657.9000001</v>
       </c>
       <c r="K251" s="5">
         <v>39098231</v>
@@ -12860,13 +12853,13 @@
         <v>35</v>
       </c>
       <c r="H252" s="5">
-        <v>2513456337.9000001</v>
+        <v>2508134931.52</v>
       </c>
       <c r="I252" s="5">
-        <v>1623074216.3699999</v>
+        <v>1651565693.1099999</v>
       </c>
       <c r="J252" s="5">
-        <v>1561628972.7</v>
+        <v>1563971657.9000001</v>
       </c>
       <c r="K252" s="5">
         <v>480804.54</v>
@@ -12898,13 +12891,13 @@
         <v>35</v>
       </c>
       <c r="H253" s="5">
-        <v>2513456337.9000001</v>
+        <v>2508134931.52</v>
       </c>
       <c r="I253" s="5">
-        <v>1623074216.3699999</v>
+        <v>1651565693.1099999</v>
       </c>
       <c r="J253" s="5">
-        <v>1561628972.7</v>
+        <v>1563971657.9000001</v>
       </c>
       <c r="K253" s="5">
         <v>10040.040000000001</v>
@@ -12936,13 +12929,13 @@
         <v>35</v>
       </c>
       <c r="H254" s="5">
-        <v>2513456337.9000001</v>
+        <v>2508134931.52</v>
       </c>
       <c r="I254" s="5">
-        <v>1623074216.3699999</v>
+        <v>1651565693.1099999</v>
       </c>
       <c r="J254" s="5">
-        <v>1561628972.7</v>
+        <v>1563971657.9000001</v>
       </c>
       <c r="K254" s="5">
         <v>2789991</v>
@@ -12974,13 +12967,13 @@
         <v>35</v>
       </c>
       <c r="H255" s="5">
-        <v>144020725.22999999</v>
+        <v>144819899.53999999</v>
       </c>
       <c r="I255" s="5">
-        <v>59104415.920000002</v>
+        <v>95915474.689999998</v>
       </c>
       <c r="J255" s="5">
-        <v>43167287.909999996</v>
+        <v>46918308.439999998</v>
       </c>
       <c r="K255" s="5">
         <v>2973874.05</v>
@@ -13012,13 +13005,13 @@
         <v>35</v>
       </c>
       <c r="H256" s="5">
-        <v>144020725.22999999</v>
+        <v>144819899.53999999</v>
       </c>
       <c r="I256" s="5">
-        <v>59104415.920000002</v>
+        <v>95915474.689999998</v>
       </c>
       <c r="J256" s="5">
-        <v>43167287.909999996</v>
+        <v>46918308.439999998</v>
       </c>
       <c r="K256" s="5">
         <v>6262083.7999999998</v>
@@ -13050,13 +13043,13 @@
         <v>35</v>
       </c>
       <c r="H257" s="5">
-        <v>144020725.22999999</v>
+        <v>144819899.53999999</v>
       </c>
       <c r="I257" s="5">
-        <v>59104415.920000002</v>
+        <v>95915474.689999998</v>
       </c>
       <c r="J257" s="5">
-        <v>43167287.909999996</v>
+        <v>46918308.439999998</v>
       </c>
       <c r="K257" s="5">
         <v>72945.570000000007</v>
@@ -13088,13 +13081,13 @@
         <v>35</v>
       </c>
       <c r="H258" s="5">
-        <v>144020725.22999999</v>
+        <v>144819899.53999999</v>
       </c>
       <c r="I258" s="5">
-        <v>59104415.920000002</v>
+        <v>95915474.689999998</v>
       </c>
       <c r="J258" s="5">
-        <v>43167287.909999996</v>
+        <v>46918308.439999998</v>
       </c>
       <c r="K258" s="5">
         <v>48552.09</v>
@@ -13286,13 +13279,13 @@
         <v>35</v>
       </c>
       <c r="H264" s="5">
-        <v>1091518068.3599999</v>
+        <v>1091518968.3599999</v>
       </c>
       <c r="I264" s="5">
-        <v>718867221.12</v>
+        <v>734928528.72000003</v>
       </c>
       <c r="J264" s="5">
-        <v>278782483.01999998</v>
+        <v>278785561.33999997</v>
       </c>
       <c r="K264" s="5">
         <v>0</v>
@@ -13324,13 +13317,13 @@
         <v>35</v>
       </c>
       <c r="H265" s="5">
-        <v>1091518068.3599999</v>
+        <v>1091518968.3599999</v>
       </c>
       <c r="I265" s="5">
-        <v>718867221.12</v>
+        <v>734928528.72000003</v>
       </c>
       <c r="J265" s="5">
-        <v>278782483.01999998</v>
+        <v>278785561.33999997</v>
       </c>
       <c r="K265" s="5">
         <v>27071.95</v>
@@ -13362,13 +13355,13 @@
         <v>35</v>
       </c>
       <c r="H266" s="5">
-        <v>1091518068.3599999</v>
+        <v>1091518968.3599999</v>
       </c>
       <c r="I266" s="5">
-        <v>718867221.12</v>
+        <v>734928528.72000003</v>
       </c>
       <c r="J266" s="5">
-        <v>278782483.01999998</v>
+        <v>278785561.33999997</v>
       </c>
       <c r="K266" s="5">
         <v>269513.28999999998</v>
@@ -13400,13 +13393,13 @@
         <v>35</v>
       </c>
       <c r="H267" s="5">
-        <v>1091518068.3599999</v>
+        <v>1091518968.3599999</v>
       </c>
       <c r="I267" s="5">
-        <v>718867221.12</v>
+        <v>734928528.72000003</v>
       </c>
       <c r="J267" s="5">
-        <v>278782483.01999998</v>
+        <v>278785561.33999997</v>
       </c>
       <c r="K267" s="5">
         <v>15371539.91</v>
@@ -13470,16 +13463,16 @@
         <v>35</v>
       </c>
       <c r="H269" s="5">
-        <v>643916822.49000001</v>
+        <v>644672754.96000004</v>
       </c>
       <c r="I269" s="5">
-        <v>288721734.68000001</v>
+        <v>289989815.35000002</v>
       </c>
       <c r="J269" s="5">
-        <v>237057324.06999999</v>
+        <v>237845404.74000001</v>
       </c>
       <c r="K269" s="5">
-        <v>20954638.09</v>
+        <v>23980911.289999999</v>
       </c>
       <c r="L269" s="6">
         <v>41404851.479999997</v>
@@ -13508,13 +13501,13 @@
         <v>35</v>
       </c>
       <c r="H270" s="5">
-        <v>643916822.49000001</v>
+        <v>644672754.96000004</v>
       </c>
       <c r="I270" s="5">
-        <v>288721734.68000001</v>
+        <v>289989815.35000002</v>
       </c>
       <c r="J270" s="5">
-        <v>237057324.06999999</v>
+        <v>237845404.74000001</v>
       </c>
       <c r="K270" s="5">
         <v>7743</v>
@@ -13546,13 +13539,13 @@
         <v>35</v>
       </c>
       <c r="H271" s="5">
-        <v>643916822.49000001</v>
+        <v>644672754.96000004</v>
       </c>
       <c r="I271" s="5">
-        <v>288721734.68000001</v>
+        <v>289989815.35000002</v>
       </c>
       <c r="J271" s="5">
-        <v>237057324.06999999</v>
+        <v>237845404.74000001</v>
       </c>
       <c r="K271" s="5">
         <v>1596270.94</v>
@@ -13584,13 +13577,13 @@
         <v>35</v>
       </c>
       <c r="H272" s="5">
-        <v>643916822.49000001</v>
+        <v>644672754.96000004</v>
       </c>
       <c r="I272" s="5">
-        <v>288721734.68000001</v>
+        <v>289989815.35000002</v>
       </c>
       <c r="J272" s="5">
-        <v>237057324.06999999</v>
+        <v>237845404.74000001</v>
       </c>
       <c r="K272" s="5">
         <v>0</v>
@@ -13654,19 +13647,19 @@
         <v>35</v>
       </c>
       <c r="H274" s="5">
-        <v>1118276489.3499999</v>
+        <v>1123261408.5899999</v>
       </c>
       <c r="I274" s="5">
-        <v>521728428.67000002</v>
+        <v>545558078.09000003</v>
       </c>
       <c r="J274" s="5">
-        <v>416193077.62</v>
+        <v>418925666.79000002</v>
       </c>
       <c r="K274" s="5">
-        <v>158832126.91999999</v>
+        <v>158911149.18000001</v>
       </c>
       <c r="L274" s="6">
-        <v>181192472.44</v>
+        <v>181215196.44</v>
       </c>
     </row>
     <row r="275" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -13692,19 +13685,19 @@
         <v>35</v>
       </c>
       <c r="H275" s="5">
-        <v>1118276489.3499999</v>
+        <v>1123261408.5899999</v>
       </c>
       <c r="I275" s="5">
-        <v>521728428.67000002</v>
+        <v>545558078.09000003</v>
       </c>
       <c r="J275" s="5">
-        <v>416193077.62</v>
+        <v>418925666.79000002</v>
       </c>
       <c r="K275" s="5">
-        <v>41427029.119999997</v>
+        <v>41595528.780000001</v>
       </c>
       <c r="L275" s="6">
-        <v>36627701.289999999</v>
+        <v>36687175.289999999</v>
       </c>
     </row>
     <row r="276" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -13730,13 +13723,13 @@
         <v>35</v>
       </c>
       <c r="H276" s="5">
-        <v>1118276489.3499999</v>
+        <v>1123261408.5899999</v>
       </c>
       <c r="I276" s="5">
-        <v>521728428.67000002</v>
+        <v>545558078.09000003</v>
       </c>
       <c r="J276" s="5">
-        <v>416193077.62</v>
+        <v>418925666.79000002</v>
       </c>
       <c r="K276" s="5">
         <v>877958</v>
@@ -13768,13 +13761,13 @@
         <v>35</v>
       </c>
       <c r="H277" s="5">
-        <v>1118276489.3499999</v>
+        <v>1123261408.5899999</v>
       </c>
       <c r="I277" s="5">
-        <v>521728428.67000002</v>
+        <v>545558078.09000003</v>
       </c>
       <c r="J277" s="5">
-        <v>416193077.62</v>
+        <v>418925666.79000002</v>
       </c>
       <c r="K277" s="5">
         <v>31459212.850000001</v>
@@ -13806,19 +13799,19 @@
         <v>35</v>
       </c>
       <c r="H278" s="5">
-        <v>1118276489.3499999</v>
+        <v>1123261408.5899999</v>
       </c>
       <c r="I278" s="5">
-        <v>521728428.67000002</v>
+        <v>545558078.09000003</v>
       </c>
       <c r="J278" s="5">
-        <v>416193077.62</v>
+        <v>418925666.79000002</v>
       </c>
       <c r="K278" s="5">
         <v>975941.94</v>
       </c>
       <c r="L278" s="6">
-        <v>1108704.8</v>
+        <v>1114873.82</v>
       </c>
     </row>
     <row r="279" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -13876,13 +13869,13 @@
         <v>35</v>
       </c>
       <c r="H280" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I280" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J280" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K280" s="5">
         <v>559000</v>
@@ -13914,13 +13907,13 @@
         <v>35</v>
       </c>
       <c r="H281" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I281" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J281" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K281" s="5">
         <v>3917373.91</v>
@@ -13952,13 +13945,13 @@
         <v>35</v>
       </c>
       <c r="H282" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I282" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J282" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K282" s="5">
         <v>2129486.3199999998</v>
@@ -13990,13 +13983,13 @@
         <v>35</v>
       </c>
       <c r="H283" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I283" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J283" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K283" s="5">
         <v>7124111.8499999996</v>
@@ -14028,13 +14021,13 @@
         <v>35</v>
       </c>
       <c r="H284" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I284" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J284" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K284" s="5">
         <v>71894.559999999998</v>
@@ -14066,13 +14059,13 @@
         <v>35</v>
       </c>
       <c r="H285" s="5">
-        <v>137517383.78999999</v>
+        <v>137517698.83000001</v>
       </c>
       <c r="I285" s="5">
-        <v>79354744.170000002</v>
+        <v>79442868.189999998</v>
       </c>
       <c r="J285" s="5">
-        <v>62514076.780000001</v>
+        <v>66812806.18</v>
       </c>
       <c r="K285" s="5">
         <v>1005499.99</v>
@@ -14104,13 +14097,13 @@
         <v>35</v>
       </c>
       <c r="H286" s="5">
-        <v>402990584.77999997</v>
+        <v>402549884.77999997</v>
       </c>
       <c r="I286" s="5">
-        <v>130833573.65000001</v>
+        <v>131410885.25</v>
       </c>
       <c r="J286" s="5">
-        <v>107990470.84</v>
+        <v>108205541.17</v>
       </c>
       <c r="K286" s="5">
         <v>58783139.479999997</v>
@@ -14142,13 +14135,13 @@
         <v>35</v>
       </c>
       <c r="H287" s="5">
-        <v>402990584.77999997</v>
+        <v>402549884.77999997</v>
       </c>
       <c r="I287" s="5">
-        <v>130833573.65000001</v>
+        <v>131410885.25</v>
       </c>
       <c r="J287" s="5">
-        <v>107990470.84</v>
+        <v>108205541.17</v>
       </c>
       <c r="K287" s="5">
         <v>1504801.25</v>
@@ -14404,13 +14397,13 @@
         <v>348</v>
       </c>
       <c r="H295" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I295" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J295" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K295" s="5">
         <v>2973.32</v>
@@ -14442,13 +14435,13 @@
         <v>348</v>
       </c>
       <c r="H296" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I296" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J296" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K296" s="5">
         <v>96694.38</v>
@@ -14480,13 +14473,13 @@
         <v>348</v>
       </c>
       <c r="H297" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I297" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J297" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K297" s="5">
         <v>9347228.25</v>
@@ -14518,13 +14511,13 @@
         <v>348</v>
       </c>
       <c r="H298" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I298" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J298" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K298" s="5">
         <v>6815.28</v>
@@ -14556,13 +14549,13 @@
         <v>348</v>
       </c>
       <c r="H299" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I299" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J299" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K299" s="5">
         <v>1371769.31</v>
@@ -14594,13 +14587,13 @@
         <v>348</v>
       </c>
       <c r="H300" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I300" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J300" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K300" s="5">
         <v>10759.68</v>
@@ -14632,13 +14625,13 @@
         <v>348</v>
       </c>
       <c r="H301" s="5">
-        <v>9534798.0600000005</v>
+        <v>9571063.7699999996</v>
       </c>
       <c r="I301" s="5">
-        <v>6314496.8099999996</v>
+        <v>6343991.21</v>
       </c>
       <c r="J301" s="5">
-        <v>4997683.5</v>
+        <v>5006258.13</v>
       </c>
       <c r="K301" s="5">
         <v>15550</v>
@@ -14670,7 +14663,7 @@
         <v>237</v>
       </c>
       <c r="H302" s="5">
-        <v>139672.75</v>
+        <v>176294.19</v>
       </c>
       <c r="I302" s="5">
         <v>128377.33</v>
@@ -14711,10 +14704,10 @@
         <v>347313.03</v>
       </c>
       <c r="I303" s="5">
-        <v>98335.53</v>
+        <v>100554.43</v>
       </c>
       <c r="J303" s="5">
-        <v>96609.73</v>
+        <v>98828.63</v>
       </c>
       <c r="K303" s="5">
         <v>1251438.8</v>
@@ -14901,7 +14894,7 @@
         <v>736047.62</v>
       </c>
       <c r="K308" s="5">
-        <v>488714.3</v>
+        <v>534884.86</v>
       </c>
       <c r="L308" s="6">
         <v>482467.95</v>
@@ -14933,10 +14926,10 @@
         <v>2183791.35</v>
       </c>
       <c r="I309" s="5">
-        <v>1639513.28</v>
+        <v>1639513.34</v>
       </c>
       <c r="J309" s="5">
-        <v>1443856.35</v>
+        <v>1443951.35</v>
       </c>
       <c r="K309" s="5">
         <v>280596.42</v>
@@ -15070,10 +15063,10 @@
         <v>268</v>
       </c>
       <c r="H313" s="5">
-        <v>13216086.9</v>
+        <v>13690134.91</v>
       </c>
       <c r="I313" s="5">
-        <v>12420966.59</v>
+        <v>12895014.6</v>
       </c>
       <c r="J313" s="5">
         <v>11695588.460000001</v>
@@ -15108,10 +15101,10 @@
         <v>268</v>
       </c>
       <c r="H314" s="5">
-        <v>13216086.9</v>
+        <v>13690134.91</v>
       </c>
       <c r="I314" s="5">
-        <v>12420966.59</v>
+        <v>12895014.6</v>
       </c>
       <c r="J314" s="5">
         <v>11695588.460000001</v>
@@ -15146,10 +15139,10 @@
         <v>268</v>
       </c>
       <c r="H315" s="5">
-        <v>13216086.9</v>
+        <v>13690134.91</v>
       </c>
       <c r="I315" s="5">
-        <v>12420966.59</v>
+        <v>12895014.6</v>
       </c>
       <c r="J315" s="5">
         <v>11695588.460000001</v>
@@ -15184,10 +15177,10 @@
         <v>268</v>
       </c>
       <c r="H316" s="5">
-        <v>13216086.9</v>
+        <v>13690134.91</v>
       </c>
       <c r="I316" s="5">
-        <v>12420966.59</v>
+        <v>12895014.6</v>
       </c>
       <c r="J316" s="5">
         <v>11695588.460000001</v>
@@ -15222,10 +15215,10 @@
         <v>268</v>
       </c>
       <c r="H317" s="5">
-        <v>13216086.9</v>
+        <v>13690134.91</v>
       </c>
       <c r="I317" s="5">
-        <v>12420966.59</v>
+        <v>12895014.6</v>
       </c>
       <c r="J317" s="5">
         <v>11695588.460000001</v>
@@ -15295,10 +15288,10 @@
         <v>9426404.0299999993</v>
       </c>
       <c r="I319" s="5">
-        <v>9050478.9199999999</v>
+        <v>9055356.5199999996</v>
       </c>
       <c r="J319" s="5">
-        <v>6296172.8099999996</v>
+        <v>6301050.4100000001</v>
       </c>
       <c r="K319" s="5">
         <v>0</v>
@@ -15333,10 +15326,10 @@
         <v>9426404.0299999993</v>
       </c>
       <c r="I320" s="5">
-        <v>9050478.9199999999</v>
+        <v>9055356.5199999996</v>
       </c>
       <c r="J320" s="5">
-        <v>6296172.8099999996</v>
+        <v>6301050.4100000001</v>
       </c>
       <c r="K320" s="5">
         <v>39918.39</v>
@@ -15403,10 +15396,10 @@
         <v>9426404.0299999993</v>
       </c>
       <c r="I322" s="5">
-        <v>9050478.9199999999</v>
+        <v>9055356.5199999996</v>
       </c>
       <c r="J322" s="5">
-        <v>6296172.8099999996</v>
+        <v>6301050.4100000001</v>
       </c>
       <c r="K322" s="5">
         <v>25269.38</v>
@@ -15441,10 +15434,10 @@
         <v>9426404.0299999993</v>
       </c>
       <c r="I323" s="5">
-        <v>9050478.9199999999</v>
+        <v>9055356.5199999996</v>
       </c>
       <c r="J323" s="5">
-        <v>6296172.8099999996</v>
+        <v>6301050.4100000001</v>
       </c>
       <c r="K323" s="5">
         <v>101501.92</v>
@@ -15479,10 +15472,10 @@
         <v>9426404.0299999993</v>
       </c>
       <c r="I324" s="5">
-        <v>9050478.9199999999</v>
+        <v>9055356.5199999996</v>
       </c>
       <c r="J324" s="5">
-        <v>6296172.8099999996</v>
+        <v>6301050.4100000001</v>
       </c>
       <c r="K324" s="5">
         <v>0</v>
@@ -15770,13 +15763,13 @@
         <v>474</v>
       </c>
       <c r="H333" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I333" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J333" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K333" s="5">
         <v>0</v>
@@ -15808,13 +15801,13 @@
         <v>474</v>
       </c>
       <c r="H334" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I334" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J334" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K334" s="5">
         <v>362708.84</v>
@@ -15846,13 +15839,13 @@
         <v>474</v>
       </c>
       <c r="H335" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I335" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J335" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K335" s="5">
         <v>0</v>
@@ -15884,13 +15877,13 @@
         <v>474</v>
       </c>
       <c r="H336" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I336" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J336" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K336" s="5">
         <v>44000</v>
@@ -15922,13 +15915,13 @@
         <v>474</v>
       </c>
       <c r="H337" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I337" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J337" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K337" s="5">
         <v>466872.54</v>
@@ -15960,13 +15953,13 @@
         <v>474</v>
       </c>
       <c r="H338" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I338" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J338" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K338" s="5">
         <v>54322.29</v>
@@ -15998,13 +15991,13 @@
         <v>474</v>
       </c>
       <c r="H339" s="5">
-        <v>70175650.920000002</v>
+        <v>70218221.569999993</v>
       </c>
       <c r="I339" s="5">
-        <v>50484148</v>
+        <v>50973254.369999997</v>
       </c>
       <c r="J339" s="5">
-        <v>45690974.25</v>
+        <v>45737504.140000001</v>
       </c>
       <c r="K339" s="5">
         <v>115410.39</v>
@@ -16162,7 +16155,7 @@
         <v>2480098.4500000002</v>
       </c>
       <c r="L343" s="6">
-        <v>3632722.55</v>
+        <v>3771885.66</v>
       </c>
     </row>
     <row r="344" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -16305,10 +16298,10 @@
         <v>3103458.03</v>
       </c>
       <c r="I347" s="5">
-        <v>3019127.56</v>
+        <v>3040690.61</v>
       </c>
       <c r="J347" s="5">
-        <v>3018564.31</v>
+        <v>3025002.85</v>
       </c>
       <c r="K347" s="5">
         <v>462035.6</v>
@@ -16343,10 +16336,10 @@
         <v>679165.53</v>
       </c>
       <c r="I348" s="5">
-        <v>275834.99</v>
+        <v>277768.59000000003</v>
       </c>
       <c r="J348" s="5">
-        <v>272469.44</v>
+        <v>274381.38</v>
       </c>
       <c r="K348" s="5">
         <v>182962.27</v>
@@ -16381,10 +16374,10 @@
         <v>679165.53</v>
       </c>
       <c r="I349" s="5">
-        <v>275834.99</v>
+        <v>277768.59000000003</v>
       </c>
       <c r="J349" s="5">
-        <v>272469.44</v>
+        <v>274381.38</v>
       </c>
       <c r="K349" s="5">
         <v>71062.98</v>
@@ -16492,13 +16485,13 @@
         <v>561</v>
       </c>
       <c r="H352" s="5">
-        <v>2790343.7</v>
+        <v>2884808.06</v>
       </c>
       <c r="I352" s="5">
-        <v>795943.01</v>
+        <v>812626.54</v>
       </c>
       <c r="J352" s="5">
-        <v>719444.53</v>
+        <v>733583.71</v>
       </c>
       <c r="K352" s="5">
         <v>518742.59</v>
@@ -16530,13 +16523,13 @@
         <v>561</v>
       </c>
       <c r="H353" s="5">
-        <v>2790343.7</v>
+        <v>2884808.06</v>
       </c>
       <c r="I353" s="5">
-        <v>795943.01</v>
+        <v>812626.54</v>
       </c>
       <c r="J353" s="5">
-        <v>719444.53</v>
+        <v>733583.71</v>
       </c>
       <c r="K353" s="5">
         <v>86666.04</v>
@@ -16568,13 +16561,13 @@
         <v>561</v>
       </c>
       <c r="H354" s="5">
-        <v>2790343.7</v>
+        <v>2884808.06</v>
       </c>
       <c r="I354" s="5">
-        <v>795943.01</v>
+        <v>812626.54</v>
       </c>
       <c r="J354" s="5">
-        <v>719444.53</v>
+        <v>733583.71</v>
       </c>
       <c r="K354" s="5">
         <v>745410.51</v>
@@ -16606,13 +16599,13 @@
         <v>561</v>
       </c>
       <c r="H355" s="5">
-        <v>2790343.7</v>
+        <v>2884808.06</v>
       </c>
       <c r="I355" s="5">
-        <v>795943.01</v>
+        <v>812626.54</v>
       </c>
       <c r="J355" s="5">
-        <v>719444.53</v>
+        <v>733583.71</v>
       </c>
       <c r="K355" s="5">
         <v>1140805.51</v>
@@ -16644,13 +16637,13 @@
         <v>561</v>
       </c>
       <c r="H356" s="5">
-        <v>2790343.7</v>
+        <v>2884808.06</v>
       </c>
       <c r="I356" s="5">
-        <v>795943.01</v>
+        <v>812626.54</v>
       </c>
       <c r="J356" s="5">
-        <v>719444.53</v>
+        <v>733583.71</v>
       </c>
       <c r="K356" s="5">
         <v>0</v>
@@ -16682,13 +16675,13 @@
         <v>561</v>
       </c>
       <c r="H357" s="5">
-        <v>747986.24</v>
+        <v>768382.69</v>
       </c>
       <c r="I357" s="5">
-        <v>545574.67000000004</v>
+        <v>551458.56999999995</v>
       </c>
       <c r="J357" s="5">
-        <v>490330.73</v>
+        <v>500094.75</v>
       </c>
       <c r="K357" s="5">
         <v>616176.53</v>
@@ -16720,13 +16713,13 @@
         <v>561</v>
       </c>
       <c r="H358" s="5">
-        <v>747986.24</v>
+        <v>768382.69</v>
       </c>
       <c r="I358" s="5">
-        <v>545574.67000000004</v>
+        <v>551458.56999999995</v>
       </c>
       <c r="J358" s="5">
-        <v>490330.73</v>
+        <v>500094.75</v>
       </c>
       <c r="K358" s="5">
         <v>46717.43</v>
@@ -16758,13 +16751,13 @@
         <v>561</v>
       </c>
       <c r="H359" s="5">
-        <v>747986.24</v>
+        <v>768382.69</v>
       </c>
       <c r="I359" s="5">
-        <v>545574.67000000004</v>
+        <v>551458.56999999995</v>
       </c>
       <c r="J359" s="5">
-        <v>490330.73</v>
+        <v>500094.75</v>
       </c>
       <c r="K359" s="5">
         <v>114706.49</v>
@@ -16799,13 +16792,13 @@
         <v>14395996.800000001</v>
       </c>
       <c r="I360" s="5">
-        <v>1887938.06</v>
+        <v>5128101.9800000004</v>
       </c>
       <c r="J360" s="5">
-        <v>1760442.9</v>
+        <v>1853398.13</v>
       </c>
       <c r="K360" s="5">
-        <v>286437.40000000002</v>
+        <v>677097.63</v>
       </c>
       <c r="L360" s="6">
         <v>283000.14</v>
@@ -16834,13 +16827,13 @@
         <v>351</v>
       </c>
       <c r="H361" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I361" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J361" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K361" s="5">
         <v>4473123.3899999997</v>
@@ -16872,13 +16865,13 @@
         <v>351</v>
       </c>
       <c r="H362" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I362" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J362" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K362" s="5">
         <v>2950732.18</v>
@@ -16910,13 +16903,13 @@
         <v>351</v>
       </c>
       <c r="H363" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I363" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J363" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K363" s="5">
         <v>1004333.8</v>
@@ -16948,13 +16941,13 @@
         <v>351</v>
       </c>
       <c r="H364" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I364" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J364" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K364" s="5">
         <v>0</v>
@@ -16986,13 +16979,13 @@
         <v>351</v>
       </c>
       <c r="H365" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I365" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J365" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K365" s="5">
         <v>17391836.789999999</v>
@@ -17024,19 +17017,19 @@
         <v>351</v>
       </c>
       <c r="H366" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I366" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J366" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K366" s="5">
         <v>20837758.469999999</v>
       </c>
       <c r="L366" s="6">
-        <v>19572476.129999999</v>
+        <v>20743888.850000001</v>
       </c>
     </row>
     <row r="367" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -17062,13 +17055,13 @@
         <v>351</v>
       </c>
       <c r="H367" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I367" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J367" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K367" s="5">
         <v>432374.12</v>
@@ -17100,13 +17093,13 @@
         <v>351</v>
       </c>
       <c r="H368" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I368" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J368" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K368" s="5">
         <v>192247.49</v>
@@ -17138,13 +17131,13 @@
         <v>351</v>
       </c>
       <c r="H369" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I369" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J369" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K369" s="5">
         <v>92853897.760000005</v>
@@ -17176,13 +17169,13 @@
         <v>351</v>
       </c>
       <c r="H370" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I370" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J370" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K370" s="5">
         <v>0</v>
@@ -17214,13 +17207,13 @@
         <v>351</v>
       </c>
       <c r="H371" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I371" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J371" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K371" s="5">
         <v>264996.52</v>
@@ -17252,16 +17245,16 @@
         <v>351</v>
       </c>
       <c r="H372" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I372" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J372" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K372" s="5">
-        <v>50307122.409999996</v>
+        <v>50307262.409999996</v>
       </c>
       <c r="L372" s="6">
         <v>56095799.780000001</v>
@@ -17290,13 +17283,13 @@
         <v>351</v>
       </c>
       <c r="H373" s="5">
-        <v>710583737.66999996</v>
+        <v>735490486.29999995</v>
       </c>
       <c r="I373" s="5">
-        <v>292239219.54000002</v>
+        <v>297795107.43000001</v>
       </c>
       <c r="J373" s="5">
-        <v>283039720.36000001</v>
+        <v>284520975.73000002</v>
       </c>
       <c r="K373" s="5">
         <v>42264087.119999997</v>
@@ -17715,7 +17708,7 @@
         <v>50530341.859999999</v>
       </c>
       <c r="I386" s="5">
-        <v>15998115.359999999</v>
+        <v>16579199.6</v>
       </c>
       <c r="J386" s="5">
         <v>14799875.75</v>
@@ -17753,7 +17746,7 @@
         <v>50530341.859999999</v>
       </c>
       <c r="I387" s="5">
-        <v>15998115.359999999</v>
+        <v>16579199.6</v>
       </c>
       <c r="J387" s="5">
         <v>14799875.75</v>
@@ -17791,7 +17784,7 @@
         <v>50530341.859999999</v>
       </c>
       <c r="I388" s="5">
-        <v>15998115.359999999</v>
+        <v>16579199.6</v>
       </c>
       <c r="J388" s="5">
         <v>14799875.75</v>
@@ -17829,7 +17822,7 @@
         <v>50530341.859999999</v>
       </c>
       <c r="I389" s="5">
-        <v>15998115.359999999</v>
+        <v>16579199.6</v>
       </c>
       <c r="J389" s="5">
         <v>14799875.75</v>
@@ -17864,13 +17857,13 @@
         <v>268</v>
       </c>
       <c r="H390" s="5">
-        <v>121264.22</v>
+        <v>121864.22</v>
       </c>
       <c r="I390" s="5">
-        <v>87389.72</v>
+        <v>92134.12</v>
       </c>
       <c r="J390" s="5">
-        <v>88159.07</v>
+        <v>92903.47</v>
       </c>
       <c r="K390" s="5">
         <v>15550.96</v>
@@ -17902,13 +17895,13 @@
         <v>268</v>
       </c>
       <c r="H391" s="5">
-        <v>121264.22</v>
+        <v>121864.22</v>
       </c>
       <c r="I391" s="5">
-        <v>87389.72</v>
+        <v>92134.12</v>
       </c>
       <c r="J391" s="5">
-        <v>88159.07</v>
+        <v>92903.47</v>
       </c>
       <c r="K391" s="5">
         <v>0</v>
@@ -17940,13 +17933,13 @@
         <v>268</v>
       </c>
       <c r="H392" s="5">
-        <v>121264.22</v>
+        <v>121864.22</v>
       </c>
       <c r="I392" s="5">
-        <v>87389.72</v>
+        <v>92134.12</v>
       </c>
       <c r="J392" s="5">
-        <v>88159.07</v>
+        <v>92903.47</v>
       </c>
       <c r="K392" s="5">
         <v>47040</v>
@@ -17981,10 +17974,10 @@
         <v>982730.65</v>
       </c>
       <c r="I393" s="5">
-        <v>695497.46</v>
+        <v>696488.81</v>
       </c>
       <c r="J393" s="5">
-        <v>696521.17</v>
+        <v>697512.52</v>
       </c>
       <c r="K393" s="5">
         <v>0</v>
@@ -18019,10 +18012,10 @@
         <v>982730.65</v>
       </c>
       <c r="I394" s="5">
-        <v>695497.46</v>
+        <v>696488.81</v>
       </c>
       <c r="J394" s="5">
-        <v>696521.17</v>
+        <v>697512.52</v>
       </c>
       <c r="K394" s="5">
         <v>20121.240000000002</v>
@@ -18057,10 +18050,10 @@
         <v>982730.65</v>
       </c>
       <c r="I395" s="5">
-        <v>695497.46</v>
+        <v>696488.81</v>
       </c>
       <c r="J395" s="5">
-        <v>696521.17</v>
+        <v>697512.52</v>
       </c>
       <c r="K395" s="5">
         <v>0</v>
@@ -18095,10 +18088,10 @@
         <v>982730.65</v>
       </c>
       <c r="I396" s="5">
-        <v>695497.46</v>
+        <v>696488.81</v>
       </c>
       <c r="J396" s="5">
-        <v>696521.17</v>
+        <v>697512.52</v>
       </c>
       <c r="K396" s="5">
         <v>69628.100000000006</v>
@@ -18784,13 +18777,13 @@
         <v>268</v>
       </c>
       <c r="H415" s="5">
-        <v>731110.15</v>
+        <v>735435.47</v>
       </c>
       <c r="I415" s="5">
-        <v>594909.51</v>
+        <v>602720.63</v>
       </c>
       <c r="J415" s="5">
-        <v>520579.42</v>
+        <v>524065.22</v>
       </c>
       <c r="K415" s="5">
         <v>100136.12</v>
@@ -18822,13 +18815,13 @@
         <v>268</v>
       </c>
       <c r="H416" s="5">
-        <v>731110.15</v>
+        <v>735435.47</v>
       </c>
       <c r="I416" s="5">
-        <v>594909.51</v>
+        <v>602720.63</v>
       </c>
       <c r="J416" s="5">
-        <v>520579.42</v>
+        <v>524065.22</v>
       </c>
       <c r="K416" s="5">
         <v>43734.36</v>
@@ -18860,19 +18853,19 @@
         <v>128</v>
       </c>
       <c r="H417" s="5">
-        <v>100518232.23999999</v>
+        <v>101148160.45</v>
       </c>
       <c r="I417" s="5">
-        <v>65572573.130000003</v>
+        <v>66541787.229999997</v>
       </c>
       <c r="J417" s="5">
-        <v>54738661.509999998</v>
+        <v>57213475.789999999</v>
       </c>
       <c r="K417" s="5">
         <v>20402755.98</v>
       </c>
       <c r="L417" s="6">
-        <v>23064255.91</v>
+        <v>23065596.030000001</v>
       </c>
     </row>
     <row r="418" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -18898,13 +18891,13 @@
         <v>128</v>
       </c>
       <c r="H418" s="5">
-        <v>100518232.23999999</v>
+        <v>101148160.45</v>
       </c>
       <c r="I418" s="5">
-        <v>65572573.130000003</v>
+        <v>66541787.229999997</v>
       </c>
       <c r="J418" s="5">
-        <v>54738661.509999998</v>
+        <v>57213475.789999999</v>
       </c>
       <c r="K418" s="5">
         <v>3249820.36</v>
@@ -18936,13 +18929,13 @@
         <v>128</v>
       </c>
       <c r="H419" s="5">
-        <v>100518232.23999999</v>
+        <v>101148160.45</v>
       </c>
       <c r="I419" s="5">
-        <v>65572573.130000003</v>
+        <v>66541787.229999997</v>
       </c>
       <c r="J419" s="5">
-        <v>54738661.509999998</v>
+        <v>57213475.789999999</v>
       </c>
       <c r="K419" s="5">
         <v>272898.02</v>
@@ -18974,19 +18967,19 @@
         <v>105</v>
       </c>
       <c r="H420" s="5">
-        <v>148697916.08000001</v>
+        <v>150526301.25</v>
       </c>
       <c r="I420" s="5">
-        <v>98541872.489999995</v>
+        <v>98832186.859999999</v>
       </c>
       <c r="J420" s="5">
-        <v>88050772.090000004</v>
+        <v>89936784.099999994</v>
       </c>
       <c r="K420" s="5">
         <v>2371321.27</v>
       </c>
       <c r="L420" s="6">
-        <v>2254887.54</v>
+        <v>2255131.48</v>
       </c>
     </row>
     <row r="421" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -19012,13 +19005,13 @@
         <v>105</v>
       </c>
       <c r="H421" s="5">
-        <v>148697916.08000001</v>
+        <v>150526301.25</v>
       </c>
       <c r="I421" s="5">
-        <v>98541872.489999995</v>
+        <v>98832186.859999999</v>
       </c>
       <c r="J421" s="5">
-        <v>88050772.090000004</v>
+        <v>89936784.099999994</v>
       </c>
       <c r="K421" s="5">
         <v>892694.59</v>
@@ -19050,19 +19043,19 @@
         <v>105</v>
       </c>
       <c r="H422" s="5">
-        <v>148697916.08000001</v>
+        <v>150526301.25</v>
       </c>
       <c r="I422" s="5">
-        <v>98541872.489999995</v>
+        <v>98832186.859999999</v>
       </c>
       <c r="J422" s="5">
-        <v>88050772.090000004</v>
+        <v>89936784.099999994</v>
       </c>
       <c r="K422" s="5">
         <v>43787426.460000001</v>
       </c>
       <c r="L422" s="6">
-        <v>38747784.229999997</v>
+        <v>38747940.329999998</v>
       </c>
     </row>
     <row r="423" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -19155,10 +19148,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I425" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J425" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K425" s="5">
         <v>87780.64</v>
@@ -19193,10 +19186,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I426" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J426" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K426" s="5">
         <v>0</v>
@@ -19231,10 +19224,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I427" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J427" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K427" s="5">
         <v>8680.33</v>
@@ -19269,10 +19262,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I428" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J428" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K428" s="5">
         <v>128756.53</v>
@@ -19307,10 +19300,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I429" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J429" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K429" s="5">
         <v>194302.66</v>
@@ -19345,10 +19338,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I430" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J430" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K430" s="5">
         <v>105757.89</v>
@@ -19383,10 +19376,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I431" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J431" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K431" s="5">
         <v>23282.7</v>
@@ -19421,10 +19414,10 @@
         <v>7054787.2599999998</v>
       </c>
       <c r="I432" s="5">
-        <v>5927215.1699999999</v>
+        <v>5934415.1699999999</v>
       </c>
       <c r="J432" s="5">
-        <v>5408551.2400000002</v>
+        <v>5417034.7400000002</v>
       </c>
       <c r="K432" s="5">
         <v>458.33</v>
@@ -19526,10 +19519,10 @@
         <v>648</v>
       </c>
       <c r="H435" s="5">
-        <v>945304.69</v>
+        <v>945474.61</v>
       </c>
       <c r="I435" s="5">
-        <v>583837.43000000005</v>
+        <v>590575.94999999995</v>
       </c>
       <c r="J435" s="5">
         <v>474380.57</v>
@@ -19564,10 +19557,10 @@
         <v>648</v>
       </c>
       <c r="H436" s="5">
-        <v>945304.69</v>
+        <v>945474.61</v>
       </c>
       <c r="I436" s="5">
-        <v>583837.43000000005</v>
+        <v>590575.94999999995</v>
       </c>
       <c r="J436" s="5">
         <v>474380.57</v>
@@ -19678,13 +19671,13 @@
         <v>196</v>
       </c>
       <c r="H439" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I439" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J439" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K439" s="5">
         <v>0</v>
@@ -19716,13 +19709,13 @@
         <v>196</v>
       </c>
       <c r="H440" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I440" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J440" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K440" s="5">
         <v>3355920.77</v>
@@ -19754,13 +19747,13 @@
         <v>196</v>
       </c>
       <c r="H441" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I441" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J441" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K441" s="5">
         <v>3348569.35</v>
@@ -19792,13 +19785,13 @@
         <v>196</v>
       </c>
       <c r="H442" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I442" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J442" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K442" s="5">
         <v>1959626.74</v>
@@ -19830,13 +19823,13 @@
         <v>196</v>
       </c>
       <c r="H443" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I443" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J443" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K443" s="5">
         <v>430886.74</v>
@@ -19868,13 +19861,13 @@
         <v>196</v>
       </c>
       <c r="H444" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I444" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J444" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K444" s="5">
         <v>46336.19</v>
@@ -19906,13 +19899,13 @@
         <v>196</v>
       </c>
       <c r="H445" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I445" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J445" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K445" s="5">
         <v>7868678.6699999999</v>
@@ -19944,13 +19937,13 @@
         <v>196</v>
       </c>
       <c r="H446" s="5">
-        <v>308010739.07999998</v>
+        <v>315454255.19999999</v>
       </c>
       <c r="I446" s="5">
-        <v>261862895.78999999</v>
+        <v>309706072.44999999</v>
       </c>
       <c r="J446" s="5">
-        <v>32574185.989999998</v>
+        <v>32575042.760000002</v>
       </c>
       <c r="K446" s="5">
         <v>2950521.63</v>
@@ -20110,10 +20103,10 @@
         <v>396</v>
       </c>
       <c r="H451" s="5">
-        <v>845850.85</v>
+        <v>846550.36</v>
       </c>
       <c r="I451" s="5">
-        <v>610428.89</v>
+        <v>631230.59</v>
       </c>
       <c r="J451" s="5">
         <v>583668.31999999995</v>
@@ -20148,10 +20141,10 @@
         <v>396</v>
       </c>
       <c r="H452" s="5">
-        <v>845850.85</v>
+        <v>846550.36</v>
       </c>
       <c r="I452" s="5">
-        <v>610428.89</v>
+        <v>631230.59</v>
       </c>
       <c r="J452" s="5">
         <v>583668.31999999995</v>
@@ -20186,10 +20179,10 @@
         <v>396</v>
       </c>
       <c r="H453" s="5">
-        <v>845850.85</v>
+        <v>846550.36</v>
       </c>
       <c r="I453" s="5">
-        <v>610428.89</v>
+        <v>631230.59</v>
       </c>
       <c r="J453" s="5">
         <v>583668.31999999995</v>
@@ -20224,10 +20217,10 @@
         <v>396</v>
       </c>
       <c r="H454" s="5">
-        <v>845850.85</v>
+        <v>846550.36</v>
       </c>
       <c r="I454" s="5">
-        <v>610428.89</v>
+        <v>631230.59</v>
       </c>
       <c r="J454" s="5">
         <v>583668.31999999995</v>
@@ -20262,10 +20255,10 @@
         <v>396</v>
       </c>
       <c r="H455" s="5">
-        <v>845850.85</v>
+        <v>846550.36</v>
       </c>
       <c r="I455" s="5">
-        <v>610428.89</v>
+        <v>631230.59</v>
       </c>
       <c r="J455" s="5">
         <v>583668.31999999995</v>
@@ -20665,7 +20658,7 @@
         <v>15977443.92</v>
       </c>
       <c r="I466" s="5">
-        <v>13023009.24</v>
+        <v>13033455.74</v>
       </c>
       <c r="J466" s="5">
         <v>12221358.73</v>
@@ -21406,7 +21399,7 @@
         <v>445</v>
       </c>
       <c r="H487" s="5">
-        <v>723857.32</v>
+        <v>784420.82</v>
       </c>
       <c r="I487" s="5">
         <v>330301.94</v>
@@ -21444,7 +21437,7 @@
         <v>445</v>
       </c>
       <c r="H488" s="5">
-        <v>723857.32</v>
+        <v>784420.82</v>
       </c>
       <c r="I488" s="5">
         <v>330301.94</v>
@@ -21482,7 +21475,7 @@
         <v>445</v>
       </c>
       <c r="H489" s="5">
-        <v>723857.32</v>
+        <v>784420.82</v>
       </c>
       <c r="I489" s="5">
         <v>330301.94</v>
@@ -21520,7 +21513,7 @@
         <v>445</v>
       </c>
       <c r="H490" s="5">
-        <v>723857.32</v>
+        <v>784420.82</v>
       </c>
       <c r="I490" s="5">
         <v>330301.94</v>
@@ -21879,7 +21872,7 @@
         <v>10406032.689999999</v>
       </c>
       <c r="I500" s="5">
-        <v>4263511.17</v>
+        <v>4271153.57</v>
       </c>
       <c r="J500" s="5">
         <v>4197885.59</v>
@@ -22077,10 +22070,10 @@
         <v>2206526.4300000002</v>
       </c>
       <c r="I506" s="5">
-        <v>1900722.97</v>
+        <v>1902012.87</v>
       </c>
       <c r="J506" s="5">
-        <v>1829491.56</v>
+        <v>1830781.46</v>
       </c>
       <c r="K506" s="5">
         <v>1179251.57</v>
@@ -22112,13 +22105,13 @@
         <v>86</v>
       </c>
       <c r="H507" s="5">
-        <v>50293625.109999999</v>
+        <v>50313625.109999999</v>
       </c>
       <c r="I507" s="5">
-        <v>23425140.260000002</v>
+        <v>23433516.260000002</v>
       </c>
       <c r="J507" s="5">
-        <v>23423299.18</v>
+        <v>23427838.780000001</v>
       </c>
       <c r="K507" s="5">
         <v>0</v>
@@ -22150,13 +22143,13 @@
         <v>86</v>
       </c>
       <c r="H508" s="5">
-        <v>50293625.109999999</v>
+        <v>50313625.109999999</v>
       </c>
       <c r="I508" s="5">
-        <v>23425140.260000002</v>
+        <v>23433516.260000002</v>
       </c>
       <c r="J508" s="5">
-        <v>23423299.18</v>
+        <v>23427838.780000001</v>
       </c>
       <c r="K508" s="5">
         <v>9772649.2799999993</v>
@@ -22188,13 +22181,13 @@
         <v>561</v>
       </c>
       <c r="H509" s="5">
-        <v>81800.759999999995</v>
+        <v>83581.36</v>
       </c>
       <c r="I509" s="5">
         <v>55535.33</v>
       </c>
       <c r="J509" s="5">
-        <v>60707.8</v>
+        <v>62299.38</v>
       </c>
       <c r="K509" s="5">
         <v>48139.34</v>
@@ -22226,13 +22219,13 @@
         <v>86</v>
       </c>
       <c r="H510" s="5">
-        <v>53902693.909999996</v>
+        <v>54399980.310000002</v>
       </c>
       <c r="I510" s="5">
-        <v>22756765.559999999</v>
+        <v>22759035.359999999</v>
       </c>
       <c r="J510" s="5">
-        <v>22758925.559999999</v>
+        <v>22761195.359999999</v>
       </c>
       <c r="K510" s="5">
         <v>770451.53</v>
@@ -22264,13 +22257,13 @@
         <v>86</v>
       </c>
       <c r="H511" s="5">
-        <v>53902693.909999996</v>
+        <v>54399980.310000002</v>
       </c>
       <c r="I511" s="5">
-        <v>22756765.559999999</v>
+        <v>22759035.359999999</v>
       </c>
       <c r="J511" s="5">
-        <v>22758925.559999999</v>
+        <v>22761195.359999999</v>
       </c>
       <c r="K511" s="5">
         <v>454393.2</v>
@@ -22302,13 +22295,13 @@
         <v>86</v>
       </c>
       <c r="H512" s="5">
-        <v>53902693.909999996</v>
+        <v>54399980.310000002</v>
       </c>
       <c r="I512" s="5">
-        <v>22756765.559999999</v>
+        <v>22759035.359999999</v>
       </c>
       <c r="J512" s="5">
-        <v>22758925.559999999</v>
+        <v>22761195.359999999</v>
       </c>
       <c r="K512" s="5">
         <v>0</v>
@@ -22340,13 +22333,13 @@
         <v>86</v>
       </c>
       <c r="H513" s="5">
-        <v>53902693.909999996</v>
+        <v>54399980.310000002</v>
       </c>
       <c r="I513" s="5">
-        <v>22756765.559999999</v>
+        <v>22759035.359999999</v>
       </c>
       <c r="J513" s="5">
-        <v>22758925.559999999</v>
+        <v>22761195.359999999</v>
       </c>
       <c r="K513" s="5">
         <v>2698010.4</v>
@@ -22378,13 +22371,13 @@
         <v>86</v>
       </c>
       <c r="H514" s="5">
-        <v>53902693.909999996</v>
+        <v>54399980.310000002</v>
       </c>
       <c r="I514" s="5">
-        <v>22756765.559999999</v>
+        <v>22759035.359999999</v>
       </c>
       <c r="J514" s="5">
-        <v>22758925.559999999</v>
+        <v>22761195.359999999</v>
       </c>
       <c r="K514" s="5">
         <v>0</v>
@@ -22774,13 +22767,13 @@
         <v>561</v>
       </c>
       <c r="H526" s="5">
-        <v>44179.03</v>
+        <v>47528.39</v>
       </c>
       <c r="I526" s="5">
-        <v>33776.75</v>
+        <v>38471.21</v>
       </c>
       <c r="J526" s="5">
-        <v>33944.449999999997</v>
+        <v>38638.910000000003</v>
       </c>
       <c r="K526" s="5">
         <v>98371.16</v>
@@ -22812,10 +22805,10 @@
         <v>56</v>
       </c>
       <c r="H527" s="5">
-        <v>117137289.95999999</v>
+        <v>140806560.88</v>
       </c>
       <c r="I527" s="5">
-        <v>98808391.090000004</v>
+        <v>139240831.84</v>
       </c>
       <c r="J527" s="5">
         <v>17152475.82</v>
@@ -22850,10 +22843,10 @@
         <v>56</v>
       </c>
       <c r="H528" s="5">
-        <v>117137289.95999999</v>
+        <v>140806560.88</v>
       </c>
       <c r="I528" s="5">
-        <v>98808391.090000004</v>
+        <v>139240831.84</v>
       </c>
       <c r="J528" s="5">
         <v>17152475.82</v>
@@ -23221,10 +23214,10 @@
         <v>4101738.58</v>
       </c>
       <c r="K538" s="5">
-        <v>4658980.9000000004</v>
+        <v>4830697.9000000004</v>
       </c>
       <c r="L538" s="6">
-        <v>4658980.9000000004</v>
+        <v>4830697.9000000004</v>
       </c>
     </row>
     <row r="539" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -23399,16 +23392,16 @@
         <v>5828665.75</v>
       </c>
       <c r="I543" s="5">
-        <v>1462632.46</v>
+        <v>1505411.17</v>
       </c>
       <c r="J543" s="5">
-        <v>1438755.78</v>
+        <v>1477807.47</v>
       </c>
       <c r="K543" s="5">
         <v>597846.16</v>
       </c>
       <c r="L543" s="6">
-        <v>459846.16</v>
+        <v>597846.16</v>
       </c>
     </row>
     <row r="544" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -23437,10 +23430,10 @@
         <v>5828665.75</v>
       </c>
       <c r="I544" s="5">
-        <v>1462632.46</v>
+        <v>1505411.17</v>
       </c>
       <c r="J544" s="5">
-        <v>1438755.78</v>
+        <v>1477807.47</v>
       </c>
       <c r="K544" s="5">
         <v>13928.75</v>
@@ -23475,16 +23468,16 @@
         <v>5828665.75</v>
       </c>
       <c r="I545" s="5">
-        <v>1462632.46</v>
+        <v>1505411.17</v>
       </c>
       <c r="J545" s="5">
-        <v>1438755.78</v>
+        <v>1477807.47</v>
       </c>
       <c r="K545" s="5">
         <v>20283035.699999999</v>
       </c>
       <c r="L545" s="6">
-        <v>18734610.370000001</v>
+        <v>19068078.07</v>
       </c>
     </row>
     <row r="546" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -23513,10 +23506,10 @@
         <v>5828665.75</v>
       </c>
       <c r="I546" s="5">
-        <v>1462632.46</v>
+        <v>1505411.17</v>
       </c>
       <c r="J546" s="5">
-        <v>1438755.78</v>
+        <v>1477807.47</v>
       </c>
       <c r="K546" s="5">
         <v>304907.65000000002</v>
@@ -23726,13 +23719,13 @@
         <v>152</v>
       </c>
       <c r="H552" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I552" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J552" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K552" s="5">
         <v>661581.93000000005</v>
@@ -23764,13 +23757,13 @@
         <v>152</v>
       </c>
       <c r="H553" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I553" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J553" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K553" s="5">
         <v>4289238.22</v>
@@ -23802,19 +23795,19 @@
         <v>152</v>
       </c>
       <c r="H554" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I554" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J554" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K554" s="5">
-        <v>98911330.599999994</v>
+        <v>99385367.920000002</v>
       </c>
       <c r="L554" s="6">
-        <v>97217862.319999993</v>
+        <v>97264412.599999994</v>
       </c>
     </row>
     <row r="555" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -23840,13 +23833,13 @@
         <v>152</v>
       </c>
       <c r="H555" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I555" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J555" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K555" s="5">
         <v>2496645.81</v>
@@ -23878,13 +23871,13 @@
         <v>152</v>
       </c>
       <c r="H556" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I556" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J556" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K556" s="5">
         <v>0</v>
@@ -23916,19 +23909,19 @@
         <v>152</v>
       </c>
       <c r="H557" s="5">
-        <v>634270676.74000001</v>
+        <v>634697473.86000001</v>
       </c>
       <c r="I557" s="5">
-        <v>408980165.54000002</v>
+        <v>409266717.60000002</v>
       </c>
       <c r="J557" s="5">
-        <v>374697506.43000001</v>
+        <v>374870137.81</v>
       </c>
       <c r="K557" s="5">
         <v>5122186.38</v>
       </c>
       <c r="L557" s="6">
-        <v>5419948.4400000004</v>
+        <v>5444542.5599999996</v>
       </c>
     </row>
     <row r="558" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -23957,7 +23950,7 @@
         <v>794658.84</v>
       </c>
       <c r="I558" s="5">
-        <v>722966.2</v>
+        <v>765312.71</v>
       </c>
       <c r="J558" s="5">
         <v>631880.27</v>
@@ -23995,7 +23988,7 @@
         <v>794658.84</v>
       </c>
       <c r="I559" s="5">
-        <v>722966.2</v>
+        <v>765312.71</v>
       </c>
       <c r="J559" s="5">
         <v>631880.27</v>
@@ -24033,7 +24026,7 @@
         <v>794658.84</v>
       </c>
       <c r="I560" s="5">
-        <v>722966.2</v>
+        <v>765312.71</v>
       </c>
       <c r="J560" s="5">
         <v>631880.27</v>
@@ -24068,13 +24061,13 @@
         <v>455</v>
       </c>
       <c r="H561" s="5">
-        <v>1182574.97</v>
+        <v>1186463.27</v>
       </c>
       <c r="I561" s="5">
-        <v>711443.63</v>
+        <v>743413.73</v>
       </c>
       <c r="J561" s="5">
-        <v>690235.7</v>
+        <v>692605.8</v>
       </c>
       <c r="K561" s="5">
         <v>72373.7</v>
@@ -24106,13 +24099,13 @@
         <v>455</v>
       </c>
       <c r="H562" s="5">
-        <v>1182574.97</v>
+        <v>1186463.27</v>
       </c>
       <c r="I562" s="5">
-        <v>711443.63</v>
+        <v>743413.73</v>
       </c>
       <c r="J562" s="5">
-        <v>690235.7</v>
+        <v>692605.8</v>
       </c>
       <c r="K562" s="5">
         <v>2494.58</v>
@@ -24144,13 +24137,13 @@
         <v>455</v>
       </c>
       <c r="H563" s="5">
-        <v>1182574.97</v>
+        <v>1186463.27</v>
       </c>
       <c r="I563" s="5">
-        <v>711443.63</v>
+        <v>743413.73</v>
       </c>
       <c r="J563" s="5">
-        <v>690235.7</v>
+        <v>692605.8</v>
       </c>
       <c r="K563" s="5">
         <v>31325.06</v>
@@ -24182,13 +24175,13 @@
         <v>455</v>
       </c>
       <c r="H564" s="5">
-        <v>1182574.97</v>
+        <v>1186463.27</v>
       </c>
       <c r="I564" s="5">
-        <v>711443.63</v>
+        <v>743413.73</v>
       </c>
       <c r="J564" s="5">
-        <v>690235.7</v>
+        <v>692605.8</v>
       </c>
       <c r="K564" s="5">
         <v>119115.02</v>
@@ -24524,13 +24517,13 @@
         <v>839</v>
       </c>
       <c r="H573" s="5">
-        <v>16253745.640000001</v>
+        <v>16916519.640000001</v>
       </c>
       <c r="I573" s="5">
-        <v>3873125.58</v>
+        <v>4143592</v>
       </c>
       <c r="J573" s="5">
-        <v>2694827.53</v>
+        <v>2822568.13</v>
       </c>
       <c r="K573" s="5">
         <v>29515912.370000001</v>
@@ -24565,7 +24558,7 @@
         <v>29094856.260000002</v>
       </c>
       <c r="I574" s="5">
-        <v>21721922.809999999</v>
+        <v>22398222.809999999</v>
       </c>
       <c r="J574" s="5">
         <v>15398943.58</v>
@@ -24603,7 +24596,7 @@
         <v>29094856.260000002</v>
       </c>
       <c r="I575" s="5">
-        <v>21721922.809999999</v>
+        <v>22398222.809999999</v>
       </c>
       <c r="J575" s="5">
         <v>15398943.58</v>
@@ -24641,7 +24634,7 @@
         <v>29094856.260000002</v>
       </c>
       <c r="I576" s="5">
-        <v>21721922.809999999</v>
+        <v>22398222.809999999</v>
       </c>
       <c r="J576" s="5">
         <v>15398943.58</v>
@@ -24679,7 +24672,7 @@
         <v>29094856.260000002</v>
       </c>
       <c r="I577" s="5">
-        <v>21721922.809999999</v>
+        <v>22398222.809999999</v>
       </c>
       <c r="J577" s="5">
         <v>15398943.58</v>
@@ -24778,13 +24771,13 @@
         <v>255</v>
       </c>
       <c r="H580" s="5">
-        <v>165985923.74000001</v>
+        <v>166265062.75</v>
       </c>
       <c r="I580" s="5">
-        <v>151458770.53</v>
+        <v>151765029.62</v>
       </c>
       <c r="J580" s="5">
-        <v>146095371.03</v>
+        <v>146107249.30000001</v>
       </c>
       <c r="K580" s="5">
         <v>10947.49</v>
@@ -24816,16 +24809,16 @@
         <v>255</v>
       </c>
       <c r="H581" s="5">
-        <v>165985923.74000001</v>
+        <v>166265062.75</v>
       </c>
       <c r="I581" s="5">
-        <v>151458770.53</v>
+        <v>151765029.62</v>
       </c>
       <c r="J581" s="5">
-        <v>146095371.03</v>
+        <v>146107249.30000001</v>
       </c>
       <c r="K581" s="5">
-        <v>24896701.32</v>
+        <v>24919834.649999999</v>
       </c>
       <c r="L581" s="6">
         <v>25798170.57</v>
@@ -24854,7 +24847,7 @@
         <v>255</v>
       </c>
       <c r="H582" s="5">
-        <v>91091283.599999994</v>
+        <v>91095181.560000002</v>
       </c>
       <c r="I582" s="5">
         <v>91038679.299999997</v>
@@ -24892,7 +24885,7 @@
         <v>255</v>
       </c>
       <c r="H583" s="5">
-        <v>91091283.599999994</v>
+        <v>91095181.560000002</v>
       </c>
       <c r="I583" s="5">
         <v>91038679.299999997</v>
@@ -24930,13 +24923,13 @@
         <v>255</v>
       </c>
       <c r="H584" s="5">
-        <v>2938080757.8800001</v>
+        <v>2941703709.5799999</v>
       </c>
       <c r="I584" s="5">
-        <v>2779096566.8800001</v>
+        <v>2781666874.0300002</v>
       </c>
       <c r="J584" s="5">
-        <v>2765256583.5500002</v>
+        <v>2765536820.3000002</v>
       </c>
       <c r="K584" s="5">
         <v>1105174.54</v>
@@ -24968,16 +24961,16 @@
         <v>255</v>
       </c>
       <c r="H585" s="5">
-        <v>2938080757.8800001</v>
+        <v>2941703709.5799999</v>
       </c>
       <c r="I585" s="5">
-        <v>2779096566.8800001</v>
+        <v>2781666874.0300002</v>
       </c>
       <c r="J585" s="5">
-        <v>2765256583.5500002</v>
+        <v>2765536820.3000002</v>
       </c>
       <c r="K585" s="5">
-        <v>1053814.3899999999</v>
+        <v>1054074.3899999999</v>
       </c>
       <c r="L585" s="6">
         <v>1534166.67</v>
@@ -25006,16 +24999,16 @@
         <v>255</v>
       </c>
       <c r="H586" s="5">
-        <v>2938080757.8800001</v>
+        <v>2941703709.5799999</v>
       </c>
       <c r="I586" s="5">
-        <v>2779096566.8800001</v>
+        <v>2781666874.0300002</v>
       </c>
       <c r="J586" s="5">
-        <v>2765256583.5500002</v>
+        <v>2765536820.3000002</v>
       </c>
       <c r="K586" s="5">
-        <v>91092226.089999899</v>
+        <v>91339407.589999899</v>
       </c>
       <c r="L586" s="6">
         <v>83510778.480000004</v>
@@ -25044,19 +25037,19 @@
         <v>255</v>
       </c>
       <c r="H587" s="5">
-        <v>2938080757.8800001</v>
+        <v>2941703709.5799999</v>
       </c>
       <c r="I587" s="5">
-        <v>2779096566.8800001</v>
+        <v>2781666874.0300002</v>
       </c>
       <c r="J587" s="5">
-        <v>2765256583.5500002</v>
+        <v>2765536820.3000002</v>
       </c>
       <c r="K587" s="5">
-        <v>13138576.439999999</v>
+        <v>13179270.439999999</v>
       </c>
       <c r="L587" s="6">
-        <v>12646360.59</v>
+        <v>12661605.43</v>
       </c>
     </row>
     <row r="588" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -25082,16 +25075,16 @@
         <v>255</v>
       </c>
       <c r="H588" s="5">
-        <v>2938080757.8800001</v>
+        <v>2941703709.5799999</v>
       </c>
       <c r="I588" s="5">
-        <v>2779096566.8800001</v>
+        <v>2781666874.0300002</v>
       </c>
       <c r="J588" s="5">
-        <v>2765256583.5500002</v>
+        <v>2765536820.3000002</v>
       </c>
       <c r="K588" s="5">
-        <v>14440473.560000001</v>
+        <v>14440994.4</v>
       </c>
       <c r="L588" s="6">
         <v>20736080.989999998</v>
@@ -25359,7 +25352,7 @@
         <v>7771025.3099999996</v>
       </c>
       <c r="I596" s="5">
-        <v>5679328.1699999999</v>
+        <v>5704357.4400000004</v>
       </c>
       <c r="J596" s="5">
         <v>4983656.5</v>
@@ -25397,7 +25390,7 @@
         <v>7771025.3099999996</v>
       </c>
       <c r="I597" s="5">
-        <v>5679328.1699999999</v>
+        <v>5704357.4400000004</v>
       </c>
       <c r="J597" s="5">
         <v>4983656.5</v>
@@ -25435,7 +25428,7 @@
         <v>31331119.829999998</v>
       </c>
       <c r="I598" s="5">
-        <v>27548180.210000001</v>
+        <v>27646380.210000001</v>
       </c>
       <c r="J598" s="5">
         <v>25062587.109999999</v>
@@ -25473,7 +25466,7 @@
         <v>31331119.829999998</v>
       </c>
       <c r="I599" s="5">
-        <v>27548180.210000001</v>
+        <v>27646380.210000001</v>
       </c>
       <c r="J599" s="5">
         <v>25062587.109999999</v>
@@ -25511,7 +25504,7 @@
         <v>31331119.829999998</v>
       </c>
       <c r="I600" s="5">
-        <v>27548180.210000001</v>
+        <v>27646380.210000001</v>
       </c>
       <c r="J600" s="5">
         <v>25062587.109999999</v>
@@ -25549,7 +25542,7 @@
         <v>31331119.829999998</v>
       </c>
       <c r="I601" s="5">
-        <v>27548180.210000001</v>
+        <v>27646380.210000001</v>
       </c>
       <c r="J601" s="5">
         <v>25062587.109999999</v>
@@ -25587,7 +25580,7 @@
         <v>31331119.829999998</v>
       </c>
       <c r="I602" s="5">
-        <v>27548180.210000001</v>
+        <v>27646380.210000001</v>
       </c>
       <c r="J602" s="5">
         <v>25062587.109999999</v>
@@ -26050,13 +26043,13 @@
         <v>152</v>
       </c>
       <c r="H616" s="5">
-        <v>123593227.64</v>
+        <v>124293631.62</v>
       </c>
       <c r="I616" s="5">
-        <v>66971090.789999999</v>
+        <v>67048110.200000003</v>
       </c>
       <c r="J616" s="5">
-        <v>65704316.289999999</v>
+        <v>65704450.560000002</v>
       </c>
       <c r="K616" s="5">
         <v>1276364.9099999999</v>
@@ -26088,13 +26081,13 @@
         <v>152</v>
       </c>
       <c r="H617" s="5">
-        <v>123593227.64</v>
+        <v>124293631.62</v>
       </c>
       <c r="I617" s="5">
-        <v>66971090.789999999</v>
+        <v>67048110.200000003</v>
       </c>
       <c r="J617" s="5">
-        <v>65704316.289999999</v>
+        <v>65704450.560000002</v>
       </c>
       <c r="K617" s="5">
         <v>0</v>
@@ -26126,13 +26119,13 @@
         <v>152</v>
       </c>
       <c r="H618" s="5">
-        <v>123593227.64</v>
+        <v>124293631.62</v>
       </c>
       <c r="I618" s="5">
-        <v>66971090.789999999</v>
+        <v>67048110.200000003</v>
       </c>
       <c r="J618" s="5">
-        <v>65704316.289999999</v>
+        <v>65704450.560000002</v>
       </c>
       <c r="K618" s="5">
         <v>86166.85</v>
@@ -26167,10 +26160,10 @@
         <v>15442206.369999999</v>
       </c>
       <c r="I619" s="5">
-        <v>6095006.75</v>
+        <v>6442632.6600000001</v>
       </c>
       <c r="J619" s="5">
-        <v>3606536.38</v>
+        <v>4035882.37</v>
       </c>
       <c r="K619" s="5">
         <v>272331.3</v>
@@ -26205,10 +26198,10 @@
         <v>15442206.369999999</v>
       </c>
       <c r="I620" s="5">
-        <v>6095006.75</v>
+        <v>6442632.6600000001</v>
       </c>
       <c r="J620" s="5">
-        <v>3606536.38</v>
+        <v>4035882.37</v>
       </c>
       <c r="K620" s="5">
         <v>6641496.4100000001</v>
@@ -26243,10 +26236,10 @@
         <v>15442206.369999999</v>
       </c>
       <c r="I621" s="5">
-        <v>6095006.75</v>
+        <v>6442632.6600000001</v>
       </c>
       <c r="J621" s="5">
-        <v>3606536.38</v>
+        <v>4035882.37</v>
       </c>
       <c r="K621" s="5">
         <v>1301745.05</v>
@@ -26281,10 +26274,10 @@
         <v>15442206.369999999</v>
       </c>
       <c r="I622" s="5">
-        <v>6095006.75</v>
+        <v>6442632.6600000001</v>
       </c>
       <c r="J622" s="5">
-        <v>3606536.38</v>
+        <v>4035882.37</v>
       </c>
       <c r="K622" s="5">
         <v>221487.88</v>
@@ -26316,10 +26309,10 @@
         <v>268</v>
       </c>
       <c r="H623" s="5">
-        <v>1867084.26</v>
+        <v>1959665.26</v>
       </c>
       <c r="I623" s="5">
-        <v>1859214.23</v>
+        <v>1951795.23</v>
       </c>
       <c r="J623" s="5">
         <v>1859552.93</v>
@@ -26357,10 +26350,10 @@
         <v>28375322.100000001</v>
       </c>
       <c r="I624" s="5">
-        <v>16627777.789999999</v>
+        <v>18152991.25</v>
       </c>
       <c r="J624" s="5">
-        <v>10420326.529999999</v>
+        <v>10469182.310000001</v>
       </c>
       <c r="K624" s="5">
         <v>1421890.92</v>
@@ -26395,10 +26388,10 @@
         <v>28375322.100000001</v>
       </c>
       <c r="I625" s="5">
-        <v>16627777.789999999</v>
+        <v>18152991.25</v>
       </c>
       <c r="J625" s="5">
-        <v>10420326.529999999</v>
+        <v>10469182.310000001</v>
       </c>
       <c r="K625" s="5">
         <v>6205176</v>
@@ -26433,13 +26426,13 @@
         <v>28375322.100000001</v>
       </c>
       <c r="I626" s="5">
-        <v>16627777.789999999</v>
+        <v>18152991.25</v>
       </c>
       <c r="J626" s="5">
-        <v>10420326.529999999</v>
+        <v>10469182.310000001</v>
       </c>
       <c r="K626" s="5">
-        <v>2895257.61</v>
+        <v>2895784.97</v>
       </c>
       <c r="L626" s="6">
         <v>2588339.92</v>
@@ -26471,10 +26464,10 @@
         <v>28375322.100000001</v>
       </c>
       <c r="I627" s="5">
-        <v>16627777.789999999</v>
+        <v>18152991.25</v>
       </c>
       <c r="J627" s="5">
-        <v>10420326.529999999</v>
+        <v>10469182.310000001</v>
       </c>
       <c r="K627" s="5">
         <v>645573.14</v>
@@ -26506,10 +26499,10 @@
         <v>899</v>
       </c>
       <c r="H628" s="5">
-        <v>1519438.46</v>
+        <v>1559438.46</v>
       </c>
       <c r="I628" s="5">
-        <v>445475.97</v>
+        <v>471325.43</v>
       </c>
       <c r="J628" s="5">
         <v>376110.07</v>
@@ -26946,19 +26939,19 @@
         <v>899</v>
       </c>
       <c r="H641" s="5">
-        <v>9432357.6500000004</v>
+        <v>9729345.5500000007</v>
       </c>
       <c r="I641" s="5">
-        <v>2744041.4</v>
+        <v>2842617.48</v>
       </c>
       <c r="J641" s="5">
-        <v>2064508.05</v>
+        <v>2096904.67</v>
       </c>
       <c r="K641" s="5">
         <v>7246393.1600000001</v>
       </c>
       <c r="L641" s="6">
-        <v>7227005.2199999997</v>
+        <v>7231854.2300000004</v>
       </c>
     </row>
     <row r="642" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -27016,19 +27009,19 @@
         <v>899</v>
       </c>
       <c r="H643" s="5">
-        <v>16222925.41</v>
+        <v>16635676.390000001</v>
       </c>
       <c r="I643" s="5">
-        <v>5734813.7199999997</v>
+        <v>6200347.1500000004</v>
       </c>
       <c r="J643" s="5">
-        <v>4352760.75</v>
+        <v>4396188.51</v>
       </c>
       <c r="K643" s="5">
         <v>3659609.15</v>
       </c>
       <c r="L643" s="6">
-        <v>4491347.8</v>
+        <v>4495796.43</v>
       </c>
     </row>
     <row r="644" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -27182,19 +27175,19 @@
         <v>899</v>
       </c>
       <c r="H648" s="5">
-        <v>126763322.11</v>
+        <v>127755484.01000001</v>
       </c>
       <c r="I648" s="5">
-        <v>63341255.729999997</v>
+        <v>63898429.390000001</v>
       </c>
       <c r="J648" s="5">
-        <v>58614844.869999997</v>
+        <v>60811279.280000001</v>
       </c>
       <c r="K648" s="5">
         <v>116385655.08</v>
       </c>
       <c r="L648" s="6">
-        <v>115678992.34999999</v>
+        <v>115681216.67</v>
       </c>
     </row>
     <row r="649" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -27220,19 +27213,19 @@
         <v>899</v>
       </c>
       <c r="H649" s="5">
-        <v>126763322.11</v>
+        <v>127755484.01000001</v>
       </c>
       <c r="I649" s="5">
-        <v>63341255.729999997</v>
+        <v>63898429.390000001</v>
       </c>
       <c r="J649" s="5">
-        <v>58614844.869999997</v>
+        <v>60811279.280000001</v>
       </c>
       <c r="K649" s="5">
-        <v>8148565.5800000001</v>
+        <v>8195411.4900000002</v>
       </c>
       <c r="L649" s="6">
-        <v>9190143.8200000003</v>
+        <v>9199132.9299999997</v>
       </c>
     </row>
     <row r="650" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -27561,10 +27554,10 @@
         <v>61449926.539999999</v>
       </c>
       <c r="I659" s="5">
-        <v>36999547.439999998</v>
+        <v>37297493.270000003</v>
       </c>
       <c r="J659" s="5">
-        <v>23634998.98</v>
+        <v>23762436.57</v>
       </c>
       <c r="K659" s="5">
         <v>478620.4</v>
@@ -27599,10 +27592,10 @@
         <v>61449926.539999999</v>
       </c>
       <c r="I660" s="5">
-        <v>36999547.439999998</v>
+        <v>37297493.270000003</v>
       </c>
       <c r="J660" s="5">
-        <v>23634998.98</v>
+        <v>23762436.57</v>
       </c>
       <c r="K660" s="5">
         <v>8266245.79</v>
@@ -27637,10 +27630,10 @@
         <v>61449926.539999999</v>
       </c>
       <c r="I661" s="5">
-        <v>36999547.439999998</v>
+        <v>37297493.270000003</v>
       </c>
       <c r="J661" s="5">
-        <v>23634998.98</v>
+        <v>23762436.57</v>
       </c>
       <c r="K661" s="5">
         <v>1373837.81</v>
@@ -27675,10 +27668,10 @@
         <v>61449926.539999999</v>
       </c>
       <c r="I662" s="5">
-        <v>36999547.439999998</v>
+        <v>37297493.270000003</v>
       </c>
       <c r="J662" s="5">
-        <v>23634998.98</v>
+        <v>23762436.57</v>
       </c>
       <c r="K662" s="5">
         <v>893059.3</v>
@@ -28295,7 +28288,7 @@
         <v>5352708.6100000003</v>
       </c>
       <c r="I681" s="5">
-        <v>3084546.55</v>
+        <v>3305481.36</v>
       </c>
       <c r="J681" s="5">
         <v>2370673.77</v>
@@ -28333,7 +28326,7 @@
         <v>5352708.6100000003</v>
       </c>
       <c r="I682" s="5">
-        <v>3084546.55</v>
+        <v>3305481.36</v>
       </c>
       <c r="J682" s="5">
         <v>2370673.77</v>
@@ -28371,13 +28364,13 @@
         <v>26082478.170000002</v>
       </c>
       <c r="I683" s="5">
-        <v>15254387.539999999</v>
+        <v>16788083.370000001</v>
       </c>
       <c r="J683" s="5">
-        <v>12374702.25</v>
+        <v>12390805.34</v>
       </c>
       <c r="K683" s="5">
-        <v>1414816.59</v>
+        <v>1414820.61</v>
       </c>
       <c r="L683" s="6">
         <v>2189024.88</v>
@@ -28409,10 +28402,10 @@
         <v>26082478.170000002</v>
       </c>
       <c r="I684" s="5">
-        <v>15254387.539999999</v>
+        <v>16788083.370000001</v>
       </c>
       <c r="J684" s="5">
-        <v>12374702.25</v>
+        <v>12390805.34</v>
       </c>
       <c r="K684" s="5">
         <v>29829</v>
@@ -28447,10 +28440,10 @@
         <v>26082478.170000002</v>
       </c>
       <c r="I685" s="5">
-        <v>15254387.539999999</v>
+        <v>16788083.370000001</v>
       </c>
       <c r="J685" s="5">
-        <v>12374702.25</v>
+        <v>12390805.34</v>
       </c>
       <c r="K685" s="5">
         <v>1806025.34</v>
@@ -28491,7 +28484,7 @@
         <v>168660.87</v>
       </c>
       <c r="K686" s="5">
-        <v>923018.1</v>
+        <v>929462.79</v>
       </c>
       <c r="L686" s="6">
         <v>886712.42</v>
@@ -28555,7 +28548,7 @@
         <v>107624846.22</v>
       </c>
       <c r="I688" s="5">
-        <v>86502189.459999993</v>
+        <v>89031918.409999996</v>
       </c>
       <c r="J688" s="5">
         <v>76983740.709999993</v>
@@ -28593,7 +28586,7 @@
         <v>107624846.22</v>
       </c>
       <c r="I689" s="5">
-        <v>86502189.459999993</v>
+        <v>89031918.409999996</v>
       </c>
       <c r="J689" s="5">
         <v>76983740.709999993</v>
@@ -28631,7 +28624,7 @@
         <v>107624846.22</v>
       </c>
       <c r="I690" s="5">
-        <v>86502189.459999993</v>
+        <v>89031918.409999996</v>
       </c>
       <c r="J690" s="5">
         <v>76983740.709999993</v>
@@ -28669,7 +28662,7 @@
         <v>107624846.22</v>
       </c>
       <c r="I691" s="5">
-        <v>86502189.459999993</v>
+        <v>89031918.409999996</v>
       </c>
       <c r="J691" s="5">
         <v>76983740.709999993</v>
@@ -28707,7 +28700,7 @@
         <v>107624846.22</v>
       </c>
       <c r="I692" s="5">
-        <v>86502189.459999993</v>
+        <v>89031918.409999996</v>
       </c>
       <c r="J692" s="5">
         <v>76983740.709999993</v>
@@ -28902,13 +28895,13 @@
         <v>49</v>
       </c>
       <c r="H698" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I698" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J698" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K698" s="5">
         <v>1727215.67</v>
@@ -28940,13 +28933,13 @@
         <v>49</v>
       </c>
       <c r="H699" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I699" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J699" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K699" s="5">
         <v>0</v>
@@ -28978,13 +28971,13 @@
         <v>49</v>
       </c>
       <c r="H700" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I700" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J700" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K700" s="5">
         <v>0</v>
@@ -29016,13 +29009,13 @@
         <v>49</v>
       </c>
       <c r="H701" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I701" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J701" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K701" s="5">
         <v>643378.07999999996</v>
@@ -29054,13 +29047,13 @@
         <v>49</v>
       </c>
       <c r="H702" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I702" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J702" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K702" s="5">
         <v>0</v>
@@ -29092,16 +29085,16 @@
         <v>49</v>
       </c>
       <c r="H703" s="5">
-        <v>5968703339.1499996</v>
+        <v>5968959109.5900002</v>
       </c>
       <c r="I703" s="5">
-        <v>5944010004.9200001</v>
+        <v>5944550293.9399996</v>
       </c>
       <c r="J703" s="5">
-        <v>5942831457.6000004</v>
+        <v>5943016517.3599997</v>
       </c>
       <c r="K703" s="5">
-        <v>2577129.73</v>
+        <v>2616244.0699999998</v>
       </c>
       <c r="L703" s="6">
         <v>2780045.88</v>
@@ -29133,10 +29126,10 @@
         <v>408227154.69</v>
       </c>
       <c r="I704" s="5">
-        <v>401856167.49000001</v>
+        <v>401907106.69</v>
       </c>
       <c r="J704" s="5">
-        <v>401750962.99000001</v>
+        <v>401807060.69</v>
       </c>
       <c r="K704" s="5">
         <v>0</v>
@@ -29171,16 +29164,16 @@
         <v>393406.91</v>
       </c>
       <c r="I705" s="5">
-        <v>218942.3</v>
+        <v>220071.5</v>
       </c>
       <c r="J705" s="5">
-        <v>216324.05</v>
+        <v>217439.7</v>
       </c>
       <c r="K705" s="5">
-        <v>225147.72</v>
+        <v>228650.12</v>
       </c>
       <c r="L705" s="6">
-        <v>223113.21</v>
+        <v>226573.58</v>
       </c>
     </row>
     <row r="706" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -29308,13 +29301,13 @@
         <v>49</v>
       </c>
       <c r="H709" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I709" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J709" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K709" s="5">
         <v>0</v>
@@ -29346,13 +29339,13 @@
         <v>49</v>
       </c>
       <c r="H710" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I710" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J710" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K710" s="5">
         <v>27034298.07</v>
@@ -29384,13 +29377,13 @@
         <v>49</v>
       </c>
       <c r="H711" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I711" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J711" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K711" s="5">
         <v>0</v>
@@ -29422,13 +29415,13 @@
         <v>49</v>
       </c>
       <c r="H712" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I712" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J712" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K712" s="5">
         <v>0</v>
@@ -29460,13 +29453,13 @@
         <v>49</v>
       </c>
       <c r="H713" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I713" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J713" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K713" s="5">
         <v>0</v>
@@ -29498,13 +29491,13 @@
         <v>49</v>
       </c>
       <c r="H714" s="5">
-        <v>400140387.01999998</v>
+        <v>410505092.32999998</v>
       </c>
       <c r="I714" s="5">
-        <v>276707096.19</v>
+        <v>277171340.66000003</v>
       </c>
       <c r="J714" s="5">
-        <v>253627836.91</v>
+        <v>254504308.13</v>
       </c>
       <c r="K714" s="5">
         <v>5333639.7</v>
@@ -29536,13 +29529,13 @@
         <v>49</v>
       </c>
       <c r="H715" s="5">
-        <v>320304195.69</v>
+        <v>332674063.5</v>
       </c>
       <c r="I715" s="5">
-        <v>242607223.81999999</v>
+        <v>244044450.21000001</v>
       </c>
       <c r="J715" s="5">
-        <v>239712085.58000001</v>
+        <v>240083027.12</v>
       </c>
       <c r="K715" s="5">
         <v>0</v>
@@ -29574,13 +29567,13 @@
         <v>49</v>
       </c>
       <c r="H716" s="5">
-        <v>320304195.69</v>
+        <v>332674063.5</v>
       </c>
       <c r="I716" s="5">
-        <v>242607223.81999999</v>
+        <v>244044450.21000001</v>
       </c>
       <c r="J716" s="5">
-        <v>239712085.58000001</v>
+        <v>240083027.12</v>
       </c>
       <c r="K716" s="5">
         <v>9450346.2400000002</v>
@@ -29612,13 +29605,13 @@
         <v>49</v>
       </c>
       <c r="H717" s="5">
-        <v>320304195.69</v>
+        <v>332674063.5</v>
       </c>
       <c r="I717" s="5">
-        <v>242607223.81999999</v>
+        <v>244044450.21000001</v>
       </c>
       <c r="J717" s="5">
-        <v>239712085.58000001</v>
+        <v>240083027.12</v>
       </c>
       <c r="K717" s="5">
         <v>206132.02</v>
@@ -29650,13 +29643,13 @@
         <v>49</v>
       </c>
       <c r="H718" s="5">
-        <v>320304195.69</v>
+        <v>332674063.5</v>
       </c>
       <c r="I718" s="5">
-        <v>242607223.81999999</v>
+        <v>244044450.21000001</v>
       </c>
       <c r="J718" s="5">
-        <v>239712085.58000001</v>
+        <v>240083027.12</v>
       </c>
       <c r="K718" s="5">
         <v>43551806.07</v>
@@ -29816,19 +29809,19 @@
         <v>49</v>
       </c>
       <c r="H723" s="5">
-        <v>133587982.55</v>
+        <v>138234424.15000001</v>
       </c>
       <c r="I723" s="5">
-        <v>93796228.079999998</v>
+        <v>94879451.780000001</v>
       </c>
       <c r="J723" s="5">
-        <v>85179150.290000007</v>
+        <v>86447232.519999996</v>
       </c>
       <c r="K723" s="5">
         <v>6681564.1399999997</v>
       </c>
       <c r="L723" s="6">
-        <v>5639079.3399999999</v>
+        <v>5663189.7000000002</v>
       </c>
     </row>
     <row r="724" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -29854,13 +29847,13 @@
         <v>49</v>
       </c>
       <c r="H724" s="5">
-        <v>133587982.55</v>
+        <v>138234424.15000001</v>
       </c>
       <c r="I724" s="5">
-        <v>93796228.079999998</v>
+        <v>94879451.780000001</v>
       </c>
       <c r="J724" s="5">
-        <v>85179150.290000007</v>
+        <v>86447232.519999996</v>
       </c>
       <c r="K724" s="5">
         <v>24167230.75</v>
@@ -29892,13 +29885,13 @@
         <v>49</v>
       </c>
       <c r="H725" s="5">
-        <v>133587982.55</v>
+        <v>138234424.15000001</v>
       </c>
       <c r="I725" s="5">
-        <v>93796228.079999998</v>
+        <v>94879451.780000001</v>
       </c>
       <c r="J725" s="5">
-        <v>85179150.290000007</v>
+        <v>86447232.519999996</v>
       </c>
       <c r="K725" s="5">
         <v>103555</v>
@@ -30026,13 +30019,13 @@
         <v>49</v>
       </c>
       <c r="H729" s="5">
-        <v>782220866.62</v>
+        <v>782470866.62</v>
       </c>
       <c r="I729" s="5">
-        <v>781570366.62</v>
+        <v>782470866.62</v>
       </c>
       <c r="J729" s="5">
-        <v>664265055.00999999</v>
+        <v>678065095.91999996</v>
       </c>
       <c r="K729" s="5">
         <v>0</v>
@@ -35248,13 +35241,13 @@
         <v>170</v>
       </c>
       <c r="H892" s="5">
-        <v>61976547.640000001</v>
+        <v>62175179.469999999</v>
       </c>
       <c r="I892" s="5">
-        <v>58335792.090000004</v>
+        <v>58386987.68</v>
       </c>
       <c r="J892" s="5">
-        <v>56473563.799999997</v>
+        <v>57021707.909999996</v>
       </c>
       <c r="K892" s="5">
         <v>1470226.2</v>
@@ -35286,13 +35279,13 @@
         <v>105</v>
       </c>
       <c r="H893" s="5">
-        <v>215968089.58000001</v>
+        <v>215977660.62</v>
       </c>
       <c r="I893" s="5">
-        <v>198330778.97</v>
+        <v>198429537.31</v>
       </c>
       <c r="J893" s="5">
-        <v>194741533.38999999</v>
+        <v>194858417.69999999</v>
       </c>
       <c r="K893" s="5">
         <v>3320605.78</v>
@@ -35324,13 +35317,13 @@
         <v>23</v>
       </c>
       <c r="H894" s="5">
-        <v>920289613.03999996</v>
+        <v>920861836.41999996</v>
       </c>
       <c r="I894" s="5">
-        <v>907326230.08000004</v>
+        <v>907696721.14999998</v>
       </c>
       <c r="J894" s="5">
-        <v>902291391.61000001</v>
+        <v>902619498.97000003</v>
       </c>
       <c r="K894" s="5">
         <v>7382372.6900000004</v>
@@ -35362,13 +35355,13 @@
         <v>23</v>
       </c>
       <c r="H895" s="5">
-        <v>920289613.03999996</v>
+        <v>920861836.41999996</v>
       </c>
       <c r="I895" s="5">
-        <v>907326230.08000004</v>
+        <v>907696721.14999998</v>
       </c>
       <c r="J895" s="5">
-        <v>902291391.61000001</v>
+        <v>902619498.97000003</v>
       </c>
       <c r="K895" s="5">
         <v>7005630.0199999996</v>
@@ -35403,10 +35396,10 @@
         <v>13502909.619999999</v>
       </c>
       <c r="I896" s="5">
-        <v>9129588.4100000001</v>
+        <v>9131038.0700000003</v>
       </c>
       <c r="J896" s="5">
-        <v>8686231.0899999999</v>
+        <v>8694306.1199999992</v>
       </c>
       <c r="K896" s="5">
         <v>1540580.2</v>
@@ -35438,13 +35431,13 @@
         <v>105</v>
       </c>
       <c r="H897" s="5">
-        <v>215968089.58000001</v>
+        <v>215977660.62</v>
       </c>
       <c r="I897" s="5">
-        <v>198330778.97</v>
+        <v>198429537.31</v>
       </c>
       <c r="J897" s="5">
-        <v>194741533.38999999</v>
+        <v>194858417.69999999</v>
       </c>
       <c r="K897" s="5">
         <v>1573391.04</v>
@@ -35479,10 +35472,10 @@
         <v>620592104.21000004</v>
       </c>
       <c r="I898" s="5">
-        <v>617992096.08000004</v>
+        <v>617992226.20000005</v>
       </c>
       <c r="J898" s="5">
-        <v>617693055.34000003</v>
+        <v>617699169.88</v>
       </c>
       <c r="K898" s="5">
         <v>133659.78</v>
@@ -35517,10 +35510,10 @@
         <v>26771606.219999999</v>
       </c>
       <c r="I899" s="5">
-        <v>26343751.309999999</v>
+        <v>26355743.27</v>
       </c>
       <c r="J899" s="5">
-        <v>25438918.510000002</v>
+        <v>25446026.91</v>
       </c>
       <c r="K899" s="5">
         <v>113459.1</v>
@@ -35555,7 +35548,7 @@
         <v>1270358305</v>
       </c>
       <c r="I900" s="5">
-        <v>1268176375.29</v>
+        <v>1268341033.8499999</v>
       </c>
       <c r="J900" s="5">
         <v>1265930591.6800001</v>
@@ -35590,13 +35583,13 @@
         <v>268</v>
       </c>
       <c r="H901" s="5">
-        <v>24517994.43</v>
+        <v>24974927.239999998</v>
       </c>
       <c r="I901" s="5">
-        <v>24020208.039999999</v>
+        <v>24057684.02</v>
       </c>
       <c r="J901" s="5">
-        <v>23759568.23</v>
+        <v>23775941.109999999</v>
       </c>
       <c r="K901" s="5">
         <v>22021.26</v>
@@ -35628,13 +35621,13 @@
         <v>56</v>
       </c>
       <c r="H902" s="5">
-        <v>25250215.989999998</v>
+        <v>25255295.890000001</v>
       </c>
       <c r="I902" s="5">
-        <v>23720918.739999998</v>
+        <v>23733415.34</v>
       </c>
       <c r="J902" s="5">
-        <v>22765092.940000001</v>
+        <v>22768511.140000001</v>
       </c>
       <c r="K902" s="5">
         <v>5496.95</v>
@@ -35666,10 +35659,10 @@
         <v>675</v>
       </c>
       <c r="H903" s="5">
-        <v>82879784.720000103</v>
+        <v>82879784.719999999</v>
       </c>
       <c r="I903" s="5">
-        <v>81278195.490000099</v>
+        <v>81410214.769999996</v>
       </c>
       <c r="J903" s="5">
         <v>80790932.439999998</v>
@@ -35704,13 +35697,13 @@
         <v>770</v>
       </c>
       <c r="H904" s="5">
-        <v>4940889.78</v>
+        <v>4940524.18</v>
       </c>
       <c r="I904" s="5">
-        <v>4849302.62</v>
+        <v>4848937.0199999996</v>
       </c>
       <c r="J904" s="5">
-        <v>4760898.4400000004</v>
+        <v>4764873.12</v>
       </c>
       <c r="K904" s="5">
         <v>34378.25</v>
@@ -35780,13 +35773,13 @@
         <v>105</v>
       </c>
       <c r="H906" s="5">
-        <v>215968089.58000001</v>
+        <v>215977660.62</v>
       </c>
       <c r="I906" s="5">
-        <v>198330778.97</v>
+        <v>198429537.31</v>
       </c>
       <c r="J906" s="5">
-        <v>194741533.38999999</v>
+        <v>194858417.69999999</v>
       </c>
       <c r="K906" s="5">
         <v>17828.18</v>
@@ -35824,7 +35817,7 @@
         <v>13104988.460000001</v>
       </c>
       <c r="J907" s="5">
-        <v>11976934.939999999</v>
+        <v>12023049.029999999</v>
       </c>
       <c r="K907" s="5">
         <v>0</v>
@@ -35856,13 +35849,13 @@
         <v>230</v>
       </c>
       <c r="H908" s="5">
-        <v>64662291.689999998</v>
+        <v>65035062.380000003</v>
       </c>
       <c r="I908" s="5">
-        <v>63783911.479999997</v>
+        <v>63884820.219999999</v>
       </c>
       <c r="J908" s="5">
-        <v>63120121.369999997</v>
+        <v>63140986.539999999</v>
       </c>
       <c r="K908" s="5">
         <v>0</v>
@@ -35894,13 +35887,13 @@
         <v>30</v>
       </c>
       <c r="H909" s="5">
-        <v>690614147.40999997</v>
+        <v>690695092.94000006</v>
       </c>
       <c r="I909" s="5">
-        <v>677735606.67999899</v>
+        <v>678108765.82999897</v>
       </c>
       <c r="J909" s="5">
-        <v>674845689.25999999</v>
+        <v>675039267.36000001</v>
       </c>
       <c r="K909" s="5">
         <v>220259.82</v>
@@ -36008,13 +36001,13 @@
         <v>561</v>
       </c>
       <c r="H912" s="5">
-        <v>123045849.63</v>
+        <v>123058561.11</v>
       </c>
       <c r="I912" s="5">
-        <v>119597213.28</v>
+        <v>119630228.09</v>
       </c>
       <c r="J912" s="5">
-        <v>118784773.53</v>
+        <v>118859412.34</v>
       </c>
       <c r="K912" s="5">
         <v>17472.439999999999</v>
@@ -36049,10 +36042,10 @@
         <v>14997930.85</v>
       </c>
       <c r="I913" s="5">
-        <v>7667553.2000000002</v>
+        <v>7682470.29</v>
       </c>
       <c r="J913" s="5">
-        <v>7060327.3399999999</v>
+        <v>7075244.4299999997</v>
       </c>
       <c r="K913" s="5">
         <v>152964.89000000001</v>
@@ -36084,13 +36077,13 @@
         <v>35</v>
       </c>
       <c r="H914" s="5">
-        <v>474510055.41000003</v>
+        <v>474509733.86000001</v>
       </c>
       <c r="I914" s="5">
-        <v>399141493.66000003</v>
+        <v>407155967.20999998</v>
       </c>
       <c r="J914" s="5">
-        <v>335843591.13</v>
+        <v>336540613.62</v>
       </c>
       <c r="K914" s="5">
         <v>105108.39</v>
@@ -36122,13 +36115,13 @@
         <v>262</v>
       </c>
       <c r="H915" s="5">
-        <v>4232884.16</v>
+        <v>4279835.4400000004</v>
       </c>
       <c r="I915" s="5">
-        <v>4094039.97</v>
+        <v>4095303.89</v>
       </c>
       <c r="J915" s="5">
-        <v>4063891.31</v>
+        <v>4066214.25</v>
       </c>
       <c r="K915" s="5">
         <v>100928.55</v>
@@ -36160,13 +36153,13 @@
         <v>310</v>
       </c>
       <c r="H916" s="5">
-        <v>499795883.63</v>
+        <v>526290112.50999999</v>
       </c>
       <c r="I916" s="5">
-        <v>375885618.19999999</v>
+        <v>376675131.01999998</v>
       </c>
       <c r="J916" s="5">
-        <v>358843822.04000002</v>
+        <v>359587207.39999998</v>
       </c>
       <c r="K916" s="5">
         <v>531509.32999999996</v>
@@ -36239,10 +36232,10 @@
         <v>620592104.21000004</v>
       </c>
       <c r="I918" s="5">
-        <v>617992096.08000004</v>
+        <v>617992226.20000005</v>
       </c>
       <c r="J918" s="5">
-        <v>617693055.34000003</v>
+        <v>617699169.88</v>
       </c>
       <c r="K918" s="5">
         <v>618332.06999999995</v>
@@ -36312,13 +36305,13 @@
         <v>86</v>
       </c>
       <c r="H920" s="5">
-        <v>12849763.199999999</v>
+        <v>12889763.199999999</v>
       </c>
       <c r="I920" s="5">
-        <v>12237952.470000001</v>
+        <v>12239917.32</v>
       </c>
       <c r="J920" s="5">
-        <v>11610428.699999999</v>
+        <v>11612393.550000001</v>
       </c>
       <c r="K920" s="5">
         <v>673741.22</v>
@@ -36350,10 +36343,10 @@
         <v>255</v>
       </c>
       <c r="H921" s="5">
-        <v>4054635561.5799999</v>
+        <v>4054638265.6900001</v>
       </c>
       <c r="I921" s="5">
-        <v>4053924835.8000002</v>
+        <v>4053956626.4299998</v>
       </c>
       <c r="J921" s="5">
         <v>4053243652.2600002</v>
@@ -36391,10 +36384,10 @@
         <v>13295390.24</v>
       </c>
       <c r="I922" s="5">
-        <v>12907270.51</v>
+        <v>12908459.91</v>
       </c>
       <c r="J922" s="5">
-        <v>12910787.369999999</v>
+        <v>12910979.25</v>
       </c>
       <c r="K922" s="5">
         <v>25849.86</v>
@@ -36429,10 +36422,10 @@
         <v>26771606.219999999</v>
       </c>
       <c r="I923" s="5">
-        <v>26343751.309999999</v>
+        <v>26355743.27</v>
       </c>
       <c r="J923" s="5">
-        <v>25438918.510000002</v>
+        <v>25446026.91</v>
       </c>
       <c r="K923" s="5">
         <v>1068691.32</v>
@@ -36464,13 +36457,13 @@
         <v>170</v>
       </c>
       <c r="H924" s="5">
-        <v>61976547.640000001</v>
+        <v>62175179.469999999</v>
       </c>
       <c r="I924" s="5">
-        <v>58335792.090000004</v>
+        <v>58386987.68</v>
       </c>
       <c r="J924" s="5">
-        <v>56473563.799999997</v>
+        <v>57021707.909999996</v>
       </c>
       <c r="K924" s="5">
         <v>1207835.3600000001</v>
@@ -36502,13 +36495,13 @@
         <v>381</v>
       </c>
       <c r="H925" s="5">
-        <v>339384930.57999998</v>
+        <v>339385421.31</v>
       </c>
       <c r="I925" s="5">
-        <v>337912105.39999998</v>
+        <v>339284177.05000001</v>
       </c>
       <c r="J925" s="5">
-        <v>337284156.49000001</v>
+        <v>337284374.94999999</v>
       </c>
       <c r="K925" s="5">
         <v>928066.72</v>
@@ -36543,7 +36536,7 @@
         <v>1270358305</v>
       </c>
       <c r="I926" s="5">
-        <v>1268176375.29</v>
+        <v>1268341033.8499999</v>
       </c>
       <c r="J926" s="5">
         <v>1265930591.6800001</v>
@@ -36578,13 +36571,13 @@
         <v>268</v>
       </c>
       <c r="H927" s="5">
-        <v>24517994.43</v>
+        <v>24974927.239999998</v>
       </c>
       <c r="I927" s="5">
-        <v>24020208.039999999</v>
+        <v>24057684.02</v>
       </c>
       <c r="J927" s="5">
-        <v>23759568.23</v>
+        <v>23775941.109999999</v>
       </c>
       <c r="K927" s="5">
         <v>515659.81</v>
@@ -36616,13 +36609,13 @@
         <v>56</v>
       </c>
       <c r="H928" s="5">
-        <v>25250215.989999998</v>
+        <v>25255295.890000001</v>
       </c>
       <c r="I928" s="5">
-        <v>23720918.739999998</v>
+        <v>23733415.34</v>
       </c>
       <c r="J928" s="5">
-        <v>22765092.940000001</v>
+        <v>22768511.140000001</v>
       </c>
       <c r="K928" s="5">
         <v>441641.68</v>
@@ -36654,10 +36647,10 @@
         <v>675</v>
       </c>
       <c r="H929" s="5">
-        <v>82879784.720000103</v>
+        <v>82879784.719999999</v>
       </c>
       <c r="I929" s="5">
-        <v>81278195.490000099</v>
+        <v>81410214.769999996</v>
       </c>
       <c r="J929" s="5">
         <v>80790932.439999998</v>
@@ -36695,7 +36688,7 @@
         <v>1208590197.9200001</v>
       </c>
       <c r="I930" s="5">
-        <v>1207259664.4400001</v>
+        <v>1207278272.6800001</v>
       </c>
       <c r="J930" s="5">
         <v>1206661158.6199999</v>
@@ -36733,10 +36726,10 @@
         <v>27542925.41</v>
       </c>
       <c r="I931" s="5">
-        <v>27463346.309999999</v>
+        <v>27467354.920000002</v>
       </c>
       <c r="J931" s="5">
-        <v>27332268.039999999</v>
+        <v>27332376.629999999</v>
       </c>
       <c r="K931" s="5">
         <v>533583.93999999994</v>
@@ -36768,10 +36761,10 @@
         <v>212</v>
       </c>
       <c r="H932" s="5">
-        <v>8680599.4800000004</v>
+        <v>8686246.4800000004</v>
       </c>
       <c r="I932" s="5">
-        <v>7947522.3899999997</v>
+        <v>7947928.1900000004</v>
       </c>
       <c r="J932" s="5">
         <v>7856263.7999999998</v>
@@ -36806,13 +36799,13 @@
         <v>770</v>
       </c>
       <c r="H933" s="5">
-        <v>4940889.78</v>
+        <v>4940524.18</v>
       </c>
       <c r="I933" s="5">
-        <v>4849302.62</v>
+        <v>4848937.0199999996</v>
       </c>
       <c r="J933" s="5">
-        <v>4760898.4400000004</v>
+        <v>4764873.12</v>
       </c>
       <c r="K933" s="5">
         <v>0</v>
@@ -36844,13 +36837,13 @@
         <v>132</v>
       </c>
       <c r="H934" s="5">
-        <v>5752007.6699999999</v>
+        <v>5751564.5899999999</v>
       </c>
       <c r="I934" s="5">
-        <v>5602052.4699999997</v>
+        <v>5601609.3899999997</v>
       </c>
       <c r="J934" s="5">
-        <v>5603666.6399999997</v>
+        <v>5603399.3600000003</v>
       </c>
       <c r="K934" s="5">
         <v>47016.61</v>
@@ -36920,13 +36913,13 @@
         <v>105</v>
       </c>
       <c r="H936" s="5">
-        <v>215968089.58000001</v>
+        <v>215977660.62</v>
       </c>
       <c r="I936" s="5">
-        <v>198330778.97</v>
+        <v>198429537.31</v>
       </c>
       <c r="J936" s="5">
-        <v>194741533.38999999</v>
+        <v>194858417.69999999</v>
       </c>
       <c r="K936" s="5">
         <v>7183547.4400000004</v>
@@ -36996,10 +36989,10 @@
         <v>648</v>
       </c>
       <c r="H938" s="5">
-        <v>19813245.149999999</v>
+        <v>19813445.149999999</v>
       </c>
       <c r="I938" s="5">
-        <v>19577956.359999999</v>
+        <v>19578156.359999999</v>
       </c>
       <c r="J938" s="5">
         <v>19541623.710000001</v>
@@ -37040,7 +37033,7 @@
         <v>13104988.460000001</v>
       </c>
       <c r="J939" s="5">
-        <v>11976934.939999999</v>
+        <v>12023049.029999999</v>
       </c>
       <c r="K939" s="5">
         <v>1770077.48</v>
@@ -37072,10 +37065,10 @@
         <v>292</v>
       </c>
       <c r="H940" s="5">
-        <v>27288143.73</v>
+        <v>27625244.879999999</v>
       </c>
       <c r="I940" s="5">
-        <v>26793588.57</v>
+        <v>27109021.890000001</v>
       </c>
       <c r="J940" s="5">
         <v>26199791.780000001</v>
@@ -37084,7 +37077,7 @@
         <v>859115.03</v>
       </c>
       <c r="L940" s="6">
-        <v>780491.56</v>
+        <v>780547.23</v>
       </c>
     </row>
     <row r="941" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -37110,13 +37103,13 @@
         <v>230</v>
       </c>
       <c r="H941" s="5">
-        <v>64662291.689999998</v>
+        <v>65035062.380000003</v>
       </c>
       <c r="I941" s="5">
-        <v>63783911.479999997</v>
+        <v>63884820.219999999</v>
       </c>
       <c r="J941" s="5">
-        <v>63120121.369999997</v>
+        <v>63140986.539999999</v>
       </c>
       <c r="K941" s="5">
         <v>1737793.23</v>
@@ -37151,10 +37144,10 @@
         <v>10754284.609999999</v>
       </c>
       <c r="I942" s="5">
-        <v>8422431.8900000006</v>
+        <v>8443241.7400000002</v>
       </c>
       <c r="J942" s="5">
-        <v>8255089.5599999996</v>
+        <v>8264458.54</v>
       </c>
       <c r="K942" s="5">
         <v>652268.21</v>
@@ -37189,10 +37182,10 @@
         <v>1472363.37</v>
       </c>
       <c r="I943" s="5">
-        <v>1372555.3</v>
+        <v>1391106.05</v>
       </c>
       <c r="J943" s="5">
-        <v>1344969.4</v>
+        <v>1364126.45</v>
       </c>
       <c r="K943" s="5">
         <v>68381.67</v>
@@ -37224,13 +37217,13 @@
         <v>412</v>
       </c>
       <c r="H944" s="5">
-        <v>1904453.54</v>
+        <v>1926332.18</v>
       </c>
       <c r="I944" s="5">
-        <v>1749539.86</v>
+        <v>1878226.5</v>
       </c>
       <c r="J944" s="5">
-        <v>1688001.89</v>
+        <v>1796271.47</v>
       </c>
       <c r="K944" s="5">
         <v>56319.71</v>
@@ -37265,10 +37258,10 @@
         <v>14810937</v>
       </c>
       <c r="I945" s="5">
-        <v>12363647.26</v>
+        <v>12369479.15</v>
       </c>
       <c r="J945" s="5">
-        <v>11882806</v>
+        <v>11888413.460000001</v>
       </c>
       <c r="K945" s="5">
         <v>1301212.6100000001</v>
@@ -37300,13 +37293,13 @@
         <v>445</v>
       </c>
       <c r="H946" s="5">
-        <v>9725145.7100000009</v>
+        <v>9750010.1400000006</v>
       </c>
       <c r="I946" s="5">
-        <v>7002656.3700000001</v>
+        <v>7027520.7999999998</v>
       </c>
       <c r="J946" s="5">
-        <v>6508384.9500000002</v>
+        <v>6533249.3799999999</v>
       </c>
       <c r="K946" s="5">
         <v>31645.72</v>
@@ -37338,7 +37331,7 @@
         <v>783</v>
       </c>
       <c r="H947" s="5">
-        <v>5453105.2199999997</v>
+        <v>5482439.2199999997</v>
       </c>
       <c r="I947" s="5">
         <v>5271740.45</v>
@@ -37376,13 +37369,13 @@
         <v>348</v>
       </c>
       <c r="H948" s="5">
-        <v>13623397.529999999</v>
+        <v>13689866.1</v>
       </c>
       <c r="I948" s="5">
-        <v>13547679.720000001</v>
+        <v>13614148.289999999</v>
       </c>
       <c r="J948" s="5">
-        <v>13465149.92</v>
+        <v>13471264.449999999</v>
       </c>
       <c r="K948" s="5">
         <v>159459.63</v>
@@ -37414,10 +37407,10 @@
         <v>225</v>
       </c>
       <c r="H949" s="5">
-        <v>12343409.369999999</v>
+        <v>12204765.619999999</v>
       </c>
       <c r="I949" s="5">
-        <v>11635645.630000001</v>
+        <v>11635895.33</v>
       </c>
       <c r="J949" s="5">
         <v>11493044</v>
@@ -37452,19 +37445,19 @@
         <v>899</v>
       </c>
       <c r="H950" s="5">
-        <v>61306321.93</v>
+        <v>61746935.43</v>
       </c>
       <c r="I950" s="5">
-        <v>53661569.969999999</v>
+        <v>54774854.630000003</v>
       </c>
       <c r="J950" s="5">
-        <v>52000627.259999998</v>
+        <v>52005193.450000003</v>
       </c>
       <c r="K950" s="5">
         <v>2476501.73</v>
       </c>
       <c r="L950" s="6">
-        <v>3361479.87</v>
+        <v>3363704.19</v>
       </c>
     </row>
     <row r="951" spans="1:12" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -37490,13 +37483,13 @@
         <v>30</v>
       </c>
       <c r="H951" s="5">
-        <v>690614147.40999997</v>
+        <v>690695092.94000006</v>
       </c>
       <c r="I951" s="5">
-        <v>677735606.67999899</v>
+        <v>678108765.82999897</v>
       </c>
       <c r="J951" s="5">
-        <v>674845689.25999999</v>
+        <v>675039267.36000001</v>
       </c>
       <c r="K951" s="5">
         <v>8783377.4600000009</v>
@@ -37566,13 +37559,13 @@
         <v>351</v>
       </c>
       <c r="H953" s="5">
-        <v>108023853.34999999</v>
+        <v>108156017.91</v>
       </c>
       <c r="I953" s="5">
-        <v>98858519.360000104</v>
+        <v>98874636.940000102</v>
       </c>
       <c r="J953" s="5">
-        <v>87197869.849999994</v>
+        <v>87580934.140000001</v>
       </c>
       <c r="K953" s="5">
         <v>11010041.810000001</v>
@@ -37604,13 +37597,13 @@
         <v>65</v>
       </c>
       <c r="H954" s="5">
-        <v>161492121.53</v>
+        <v>161515562.12</v>
       </c>
       <c r="I954" s="5">
-        <v>160187942.06</v>
+        <v>160290391.56</v>
       </c>
       <c r="J954" s="5">
-        <v>159703084.83000001</v>
+        <v>159801759.56999999</v>
       </c>
       <c r="K954" s="5">
         <v>2650672</v>
@@ -37642,13 +37635,13 @@
         <v>109</v>
       </c>
       <c r="H955" s="5">
-        <v>11082169.529999999</v>
+        <v>11082937.9</v>
       </c>
       <c r="I955" s="5">
-        <v>10783131.17</v>
+        <v>10784519.48</v>
       </c>
       <c r="J955" s="5">
-        <v>10455242.720000001</v>
+        <v>10456631.029999999</v>
       </c>
       <c r="K955" s="5">
         <v>536592.22</v>
@@ -37718,13 +37711,13 @@
         <v>561</v>
       </c>
       <c r="H957" s="5">
-        <v>123045849.63</v>
+        <v>123058561.11</v>
       </c>
       <c r="I957" s="5">
-        <v>119597213.28</v>
+        <v>119630228.09</v>
       </c>
       <c r="J957" s="5">
-        <v>118784773.53</v>
+        <v>118859412.34</v>
       </c>
       <c r="K957" s="5">
         <v>1396800.34</v>
@@ -37756,13 +37749,13 @@
         <v>366</v>
       </c>
       <c r="H958" s="5">
-        <v>5613924.3399999999</v>
+        <v>5628924.3200000003</v>
       </c>
       <c r="I958" s="5">
-        <v>4922129.59</v>
+        <v>5006184.1100000003</v>
       </c>
       <c r="J958" s="5">
-        <v>4887716.63</v>
+        <v>4970342.38</v>
       </c>
       <c r="K958" s="5">
         <v>191625.95</v>
@@ -37908,13 +37901,13 @@
         <v>35</v>
       </c>
       <c r="H962" s="5">
-        <v>474510055.41000003</v>
+        <v>474509733.86000001</v>
       </c>
       <c r="I962" s="5">
-        <v>399141493.66000003</v>
+        <v>407155967.20999998</v>
       </c>
       <c r="J962" s="5">
-        <v>335843591.13</v>
+        <v>336540613.62</v>
       </c>
       <c r="K962" s="5">
         <v>5012189.78</v>
@@ -37946,13 +37939,13 @@
         <v>23</v>
       </c>
       <c r="H963" s="5">
-        <v>920289613.03999996</v>
+        <v>920861836.41999996</v>
       </c>
       <c r="I963" s="5">
-        <v>907326230.08000004</v>
+        <v>907696721.14999998</v>
       </c>
       <c r="J963" s="5">
-        <v>902291391.61000001</v>
+        <v>902619498.97000003</v>
       </c>
       <c r="K963" s="5">
         <v>14212566.789999999</v>
@@ -37984,13 +37977,13 @@
         <v>105</v>
       </c>
       <c r="H964" s="5">
-        <v>215968089.58000001</v>
+        <v>215977660.62</v>
       </c>
       <c r="I964" s="5">
-        <v>198330778.97</v>
+        <v>198429537.31</v>
       </c>
       <c r="J964" s="5">
-        <v>194741533.38999999</v>
+        <v>194858417.69999999</v>
       </c>
       <c r="K964" s="5">
         <v>0</v>
@@ -38022,13 +38015,13 @@
         <v>230</v>
       </c>
       <c r="H965" s="5">
-        <v>64662291.689999998</v>
+        <v>65035062.380000003</v>
       </c>
       <c r="I965" s="5">
-        <v>63783911.479999997</v>
+        <v>63884820.219999999</v>
       </c>
       <c r="J965" s="5">
-        <v>63120121.369999997</v>
+        <v>63140986.539999999</v>
       </c>
       <c r="K965" s="5">
         <v>0</v>
@@ -38060,13 +38053,13 @@
         <v>23</v>
       </c>
       <c r="H966" s="5">
-        <v>920289613.03999996</v>
+        <v>920861836.41999996</v>
       </c>
       <c r="I966" s="5">
-        <v>907326230.08000004</v>
+        <v>907696721.14999998</v>
       </c>
       <c r="J966" s="5">
-        <v>902291391.61000001</v>
+        <v>902619498.97000003</v>
       </c>
       <c r="K966" s="5">
         <v>0</v>
@@ -38101,10 +38094,10 @@
         <v>14810937</v>
       </c>
       <c r="I967" s="5">
-        <v>12363647.26</v>
+        <v>12369479.15</v>
       </c>
       <c r="J967" s="5">
-        <v>11882806</v>
+        <v>11888413.460000001</v>
       </c>
       <c r="K967" s="5">
         <v>0</v>
@@ -38136,13 +38129,13 @@
         <v>445</v>
       </c>
       <c r="H968" s="5">
-        <v>9725145.7100000009</v>
+        <v>9750010.1400000006</v>
       </c>
       <c r="I968" s="5">
-        <v>7002656.3700000001</v>
+        <v>7027520.7999999998</v>
       </c>
       <c r="J968" s="5">
-        <v>6508384.9500000002</v>
+        <v>6533249.3799999999</v>
       </c>
       <c r="K968" s="5">
         <v>0</v>
@@ -38174,13 +38167,13 @@
         <v>348</v>
       </c>
       <c r="H969" s="5">
-        <v>13623397.529999999</v>
+        <v>13689866.1</v>
       </c>
       <c r="I969" s="5">
-        <v>13547679.720000001</v>
+        <v>13614148.289999999</v>
       </c>
       <c r="J969" s="5">
-        <v>13465149.92</v>
+        <v>13471264.449999999</v>
       </c>
       <c r="K969" s="5">
         <v>0</v>
@@ -38212,10 +38205,10 @@
         <v>225</v>
       </c>
       <c r="H970" s="5">
-        <v>12343409.369999999</v>
+        <v>12204765.619999999</v>
       </c>
       <c r="I970" s="5">
-        <v>11635645.630000001</v>
+        <v>11635895.33</v>
       </c>
       <c r="J970" s="5">
         <v>11493044</v>
@@ -38250,13 +38243,13 @@
         <v>899</v>
       </c>
       <c r="H971" s="5">
-        <v>61306321.93</v>
+        <v>61746935.43</v>
       </c>
       <c r="I971" s="5">
-        <v>53661569.969999999</v>
+        <v>54774854.630000003</v>
       </c>
       <c r="J971" s="5">
-        <v>52000627.259999998</v>
+        <v>52005193.450000003</v>
       </c>
       <c r="K971" s="5">
         <v>0</v>
@@ -38288,13 +38281,13 @@
         <v>30</v>
       </c>
       <c r="H972" s="5">
-        <v>690614147.40999997</v>
+        <v>690695092.94000006</v>
       </c>
       <c r="I972" s="5">
-        <v>677735606.67999899</v>
+        <v>678108765.82999897</v>
       </c>
       <c r="J972" s="5">
-        <v>674845689.25999999</v>
+        <v>675039267.36000001</v>
       </c>
       <c r="K972" s="5">
         <v>0</v>
@@ -38364,13 +38357,13 @@
         <v>1168</v>
       </c>
       <c r="H974" s="5">
-        <v>7338197840.8900003</v>
+        <v>7338220523.8400002</v>
       </c>
       <c r="I974" s="5">
-        <v>7334070798.1499996</v>
+        <v>7334093481.1000004</v>
       </c>
       <c r="J974" s="5">
-        <v>7333952141.75</v>
+        <v>7333974808.0600004</v>
       </c>
       <c r="K974" s="5">
         <v>0</v>
@@ -38402,13 +38395,13 @@
         <v>381</v>
       </c>
       <c r="H975" s="5">
-        <v>339384930.57999998</v>
+        <v>339385421.31</v>
       </c>
       <c r="I975" s="5">
-        <v>337912105.39999998</v>
+        <v>339284177.05000001</v>
       </c>
       <c r="J975" s="5">
-        <v>337284156.49000001</v>
+        <v>337284374.94999999</v>
       </c>
       <c r="K975" s="5">
         <v>0</v>
@@ -38443,7 +38436,7 @@
         <v>1208590197.9200001</v>
       </c>
       <c r="I976" s="5">
-        <v>1207259664.4400001</v>
+        <v>1207278272.6800001</v>
       </c>
       <c r="J976" s="5">
         <v>1206661158.6199999</v>
@@ -38478,13 +38471,13 @@
         <v>1168</v>
       </c>
       <c r="H977" s="5">
-        <v>7338197840.8900003</v>
+        <v>7338220523.8400002</v>
       </c>
       <c r="I977" s="5">
-        <v>7334070798.1499996</v>
+        <v>7334093481.1000004</v>
       </c>
       <c r="J977" s="5">
-        <v>7333952141.75</v>
+        <v>7333974808.0600004</v>
       </c>
       <c r="K977" s="5">
         <v>759396.57</v>
@@ -38592,13 +38585,13 @@
         <v>310</v>
       </c>
       <c r="H980" s="5">
-        <v>499795883.63</v>
+        <v>526290112.50999999</v>
       </c>
       <c r="I980" s="5">
-        <v>375885618.19999999</v>
+        <v>376675131.01999998</v>
       </c>
       <c r="J980" s="5">
-        <v>358843822.04000002</v>
+        <v>359587207.39999998</v>
       </c>
       <c r="K980" s="5">
         <v>97.36</v>
@@ -38610,5 +38603,7 @@
     <row r="981" spans="1:12" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>